--- a/Översikt HABO.xlsx
+++ b/Översikt HABO.xlsx
@@ -601,7 +601,7 @@
         <v>45337</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>44607</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
         <v>44749</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>45534</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>45183</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>45635</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>45791</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>44877</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>45882</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>44749</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>45419</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>45534</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>45106</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>45631</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>45811</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>44824</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>45930</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>45225</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>44801</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>45635</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>45882</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>45543</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>44749</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>45597</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         <v>45635</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>45933</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>45747</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3592,7 +3592,7 @@
         <v>45985</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>44799</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>45635</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>45183</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4027,7 +4027,7 @@
         <v>45813</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>45882</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>45355</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>44847</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>44527</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44769</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>44846</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>44693</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         <v>44877</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>44640</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>44693</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>44670</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>44859</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>44727</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         <v>44500</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>44469</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>44623</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         <v>45475</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5452,7 +5452,7 @@
         <v>45212</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>45091</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>45029</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>45660</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>45641</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>45698</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>45636</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>45687</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         <v>45597</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>45030</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>45478</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>45620</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         <v>45621</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>45621</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         <v>45621</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6552,7 +6552,7 @@
         <v>44801</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6625,7 +6625,7 @@
         <v>45111</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         <v>44571</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>45475</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>45475</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>45120</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         <v>45146</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>45602</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7136,7 +7136,7 @@
         <v>44783</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>45030</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7287,7 +7287,7 @@
         <v>45595</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         <v>45595</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>44951</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>45210</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>45278</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>45475</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         <v>45621</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         <v>45621</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7871,7 +7871,7 @@
         <v>45621</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7944,7 +7944,7 @@
         <v>44896</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8017,7 +8017,7 @@
         <v>45597</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         <v>45560</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8168,7 +8168,7 @@
         <v>44799</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
         <v>45107</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8314,7 +8314,7 @@
         <v>45121</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>45149</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>44749</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         <v>44749</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>45091</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>45635</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>45646</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8825,7 +8825,7 @@
         <v>45671</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
         <v>45099</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>45099</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         <v>45111</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         <v>45469</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9190,7 +9190,7 @@
         <v>44816</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         <v>44845</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9336,7 +9336,7 @@
         <v>45887</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9409,7 +9409,7 @@
         <v>45760</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9482,7 +9482,7 @@
         <v>44474</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9555,7 +9555,7 @@
         <v>45820</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9628,7 +9628,7 @@
         <v>45882</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9706,7 +9706,7 @@
         <v>44944</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9779,7 +9779,7 @@
         <v>45896</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
         <v>44488</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         <v>45903</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9998,7 +9998,7 @@
         <v>45620</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10071,7 +10071,7 @@
         <v>44628</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10144,7 +10144,7 @@
         <v>44575</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10217,7 +10217,7 @@
         <v>45020</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10290,7 +10290,7 @@
         <v>45020</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10363,7 +10363,7 @@
         <v>45246</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10436,7 +10436,7 @@
         <v>45922</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10509,7 +10509,7 @@
         <v>45922</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10582,7 +10582,7 @@
         <v>45222</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10655,7 +10655,7 @@
         <v>45173</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
         <v>45926</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10801,7 +10801,7 @@
         <v>45558</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>45931</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10947,7 +10947,7 @@
         <v>44894</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>45469</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11098,7 +11098,7 @@
         <v>44749</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11171,7 +11171,7 @@
         <v>44749</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11244,7 +11244,7 @@
         <v>45751</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11317,7 +11317,7 @@
         <v>44628</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11390,7 +11390,7 @@
         <v>45099</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>45429</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         <v>45950</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11609,7 +11609,7 @@
         <v>45951</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11682,7 +11682,7 @@
         <v>45400</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11755,7 +11755,7 @@
         <v>45188</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
         <v>45450</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11901,7 +11901,7 @@
         <v>45597</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11979,7 +11979,7 @@
         <v>45706</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12052,7 +12052,7 @@
         <v>45120</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12125,7 +12125,7 @@
         <v>45478</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12198,7 +12198,7 @@
         <v>45972</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12271,7 +12271,7 @@
         <v>45974</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12344,7 +12344,7 @@
         <v>45020</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12417,7 +12417,7 @@
         <v>45698</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12490,7 +12490,7 @@
         <v>45698</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12563,7 +12563,7 @@
         <v>45926</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12636,7 +12636,7 @@
         <v>45985</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12714,7 +12714,7 @@
         <v>45985</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12792,7 +12792,7 @@
         <v>45982</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12865,7 +12865,7 @@
         <v>44797</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12938,7 +12938,7 @@
         <v>44913</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13011,7 +13011,7 @@
         <v>45287</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13084,7 +13084,7 @@
         <v>45419</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
         <v>45617</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>45750</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>45271</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>45638</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13449,7 +13449,7 @@
         <v>45595</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>46000</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13595,7 +13595,7 @@
         <v>46000</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13668,7 +13668,7 @@
         <v>46000</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13741,7 +13741,7 @@
         <v>46000</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>45450</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13887,7 +13887,7 @@
         <v>45450</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
         <v>45576</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14033,7 +14033,7 @@
         <v>45183</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>45996</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14179,7 +14179,7 @@
         <v>45996</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14252,7 +14252,7 @@
         <v>45271</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14325,7 +14325,7 @@
         <v>44876</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14398,7 +14398,7 @@
         <v>45242</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14476,7 +14476,7 @@
         <v>44830</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>46171</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>45677</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         <v>45218</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14768,7 +14768,7 @@
         <v>46037</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14841,7 +14841,7 @@
         <v>46037</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
         <v>45203</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14987,7 +14987,7 @@
         <v>46037</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15060,7 +15060,7 @@
         <v>46041</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15133,7 +15133,7 @@
         <v>45638</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
         <v>46043</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15279,7 +15279,7 @@
         <v>46043</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15352,7 +15352,7 @@
         <v>46043</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15425,7 +15425,7 @@
         <v>46043</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15498,7 +15498,7 @@
         <v>46043</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15571,7 +15571,7 @@
         <v>46043</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15644,7 +15644,7 @@
         <v>45733</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>45594</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15790,7 +15790,7 @@
         <v>46176</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15863,7 +15863,7 @@
         <v>46052</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>45595</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16009,7 +16009,7 @@
         <v>45470</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16082,7 +16082,7 @@
         <v>45620</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16155,7 +16155,7 @@
         <v>45620</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16228,7 +16228,7 @@
         <v>46059</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>45450</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16374,7 +16374,7 @@
         <v>45450</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16447,7 +16447,7 @@
         <v>46069</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16520,7 +16520,7 @@
         <v>45400</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16593,7 +16593,7 @@
         <v>45734</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16666,7 +16666,7 @@
         <v>45113</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16739,7 +16739,7 @@
         <v>45554</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16812,7 +16812,7 @@
         <v>45236</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16885,7 +16885,7 @@
         <v>45220</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16958,7 +16958,7 @@
         <v>46191</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17031,7 +17031,7 @@
         <v>46191</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17104,7 +17104,7 @@
         <v>46191</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17177,7 +17177,7 @@
         <v>46191</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17250,7 +17250,7 @@
         <v>45356</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>44939</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17396,7 +17396,7 @@
         <v>44995</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17469,7 +17469,7 @@
         <v>45091</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>44877</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         <v>45397</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>45307</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17761,7 +17761,7 @@
         <v>45580</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17834,7 +17834,7 @@
         <v>45007</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17907,7 +17907,7 @@
         <v>45152</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17980,7 +17980,7 @@
         <v>45510</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18053,7 +18053,7 @@
         <v>46203</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>45576</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18199,7 +18199,7 @@
         <v>45635</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18272,7 +18272,7 @@
         <v>46203</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18345,7 +18345,7 @@
         <v>46246</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>45757</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18491,7 +18491,7 @@
         <v>45757</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18564,7 +18564,7 @@
         <v>46135</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18637,7 +18637,7 @@
         <v>45698</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18710,7 +18710,7 @@
         <v>45204</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18783,7 +18783,7 @@
         <v>45595</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18856,7 +18856,7 @@
         <v>45390</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18929,7 +18929,7 @@
         <v>46202</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19002,7 +19002,7 @@
         <v>46246</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19075,7 +19075,7 @@
         <v>45631</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19148,7 +19148,7 @@
         <v>44909</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19221,7 +19221,7 @@
         <v>45372</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19294,7 +19294,7 @@
         <v>45647</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19367,7 +19367,7 @@
         <v>44488</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19440,7 +19440,7 @@
         <v>46251</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19513,7 +19513,7 @@
         <v>45636</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
         <v>45316</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19659,7 +19659,7 @@
         <v>46244</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>45594</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19805,7 +19805,7 @@
         <v>45644</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19878,7 +19878,7 @@
         <v>45120</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19951,7 +19951,7 @@
         <v>46254</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         <v>45119</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20097,7 +20097,7 @@
         <v>45119</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20170,7 +20170,7 @@
         <v>44488</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20243,7 +20243,7 @@
         <v>44488</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>46216</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20389,7 +20389,7 @@
         <v>45119</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>45152</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         <v>44995</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20608,7 +20608,7 @@
         <v>45363</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20681,7 +20681,7 @@
         <v>44914</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20754,7 +20754,7 @@
         <v>45217</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20827,7 +20827,7 @@
         <v>45106</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20900,7 +20900,7 @@
         <v>45119</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20973,7 +20973,7 @@
         <v>45120</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21046,7 +21046,7 @@
         <v>45120</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>45120</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21192,7 +21192,7 @@
         <v>45687</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21265,7 +21265,7 @@
         <v>44775</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>46267</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21411,7 +21411,7 @@
         <v>46267</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21484,7 +21484,7 @@
         <v>46268</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21557,7 +21557,7 @@
         <v>46268</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21630,7 +21630,7 @@
         <v>45777</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21703,7 +21703,7 @@
         <v>45777</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21776,7 +21776,7 @@
         <v>46268</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21849,7 +21849,7 @@
         <v>46273</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21927,7 +21927,7 @@
         <v>46273</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22005,7 +22005,7 @@
         <v>46232</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22078,7 +22078,7 @@
         <v>45789</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22151,7 +22151,7 @@
         <v>45608</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22224,7 +22224,7 @@
         <v>45364</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22297,7 +22297,7 @@
         <v>45021</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22370,7 +22370,7 @@
         <v>45734</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22443,7 +22443,7 @@
         <v>45807</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22516,7 +22516,7 @@
         <v>45810</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22589,7 +22589,7 @@
         <v>45812</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22662,7 +22662,7 @@
         <v>45811</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22735,7 +22735,7 @@
         <v>45827</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22808,7 +22808,7 @@
         <v>45827</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22881,7 +22881,7 @@
         <v>45846</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22954,7 +22954,7 @@
         <v>45810</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23027,7 +23027,7 @@
         <v>45751</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23100,7 +23100,7 @@
         <v>45877</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23173,7 +23173,7 @@
         <v>45882</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23251,7 +23251,7 @@
         <v>45882</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23324,7 +23324,7 @@
         <v>45882</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>45712</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>45712</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23543,7 +23543,7 @@
         <v>45712</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23616,7 +23616,7 @@
         <v>45737</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>

--- a/Översikt HABO.xlsx
+++ b/Översikt HABO.xlsx
@@ -601,7 +601,7 @@
         <v>45337</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>44607</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
         <v>44749</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>45534</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>45183</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>45635</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>45791</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>44877</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>45882</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>44749</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>45419</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>45534</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>45106</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>45631</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>45811</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>44824</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 47199-2025</t>
+          <t>A 38067-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2411,10 +2411,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45930</v>
+        <v>45882</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2426,8 +2426,13 @@
           <t>HABO</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2436,13 +2441,13 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>1</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2454,482 +2459,477 @@
         <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S18" t="n">
         <v>2</v>
       </c>
       <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Cypresslummer
+Torrmusseron</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/artfynd/A 38067-2025 artfynd.xlsx", "A 38067-2025")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/kartor/A 38067-2025 karta.png", "A 38067-2025")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/kartor_geotiff/A 38067-2025 georefererad karta.tif", "A 38067-2025")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/klagomål/A 38067-2025 FSC-klagomål.docx", "A 38067-2025")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/klagomålsmail/A 38067-2025 FSC-klagomål mail.docx", "A 38067-2025")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/tillsyn/A 38067-2025 tillsynsbegäran.docx", "A 38067-2025")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/tillsynsmail/A 38067-2025 tillsynsbegäran mail.docx", "A 38067-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 47199-2025</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45930</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>HABO</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
         <v>8</v>
       </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Dropptaggsvamp</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0643/artfynd/A 47199-2025 artfynd.xlsx", "A 47199-2025")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0643/kartor/A 47199-2025 karta.png", "A 47199-2025")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0643/kartor_geotiff/A 47199-2025 georefererad karta.tif", "A 47199-2025")</f>
         <v/>
       </c>
-      <c r="Z18">
+      <c r="Z19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0643/knärot/A 47199-2025 karta knärot.png", "A 47199-2025")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0643/klagomål/A 47199-2025 FSC-klagomål.docx", "A 47199-2025")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0643/klagomålsmail/A 47199-2025 FSC-klagomål mail.docx", "A 47199-2025")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0643/tillsyn/A 47199-2025 tillsynsbegäran.docx", "A 47199-2025")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0643/tillsynsmail/A 47199-2025 tillsynsbegäran mail.docx", "A 47199-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>A 52417-2023</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
         <v>45225</v>
       </c>
-      <c r="E19" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>HABO</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
+      <c r="E20" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>HABO</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J20" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
         <v>1</v>
       </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
         <v>1</v>
       </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>2</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T20" t="n">
         <v>2</v>
       </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Svinrot
 Grönvit nattviol</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0643/artfynd/A 52417-2023 artfynd.xlsx", "A 52417-2023")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0643/kartor/A 52417-2023 karta.png", "A 52417-2023")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0643/kartor_geotiff/A 52417-2023 georefererad karta.tif", "A 52417-2023")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0643/klagomål/A 52417-2023 FSC-klagomål.docx", "A 52417-2023")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0643/klagomålsmail/A 52417-2023 FSC-klagomål mail.docx", "A 52417-2023")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0643/tillsyn/A 52417-2023 tillsynsbegäran.docx", "A 52417-2023")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0643/tillsynsmail/A 52417-2023 tillsynsbegäran mail.docx", "A 52417-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>A 35775-2022</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
         <v>44801</v>
       </c>
-      <c r="E20" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>HABO</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
+      <c r="E21" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>HABO</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
         <v>0.9</v>
       </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
         <v>1</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M21" t="n">
         <v>1</v>
       </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
         <v>2</v>
       </c>
-      <c r="R20" t="n">
+      <c r="R21" t="n">
         <v>1</v>
       </c>
-      <c r="S20" t="n">
+      <c r="S21" t="n">
         <v>2</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T21" t="n">
         <v>2</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U21" t="n">
         <v>2</v>
       </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Slåttergubbe
 Svinrot</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0643/artfynd/A 35775-2022 artfynd.xlsx", "A 35775-2022")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0643/kartor/A 35775-2022 karta.png", "A 35775-2022")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0643/kartor_geotiff/A 35775-2022 georefererad karta.tif", "A 35775-2022")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0643/klagomål/A 35775-2022 FSC-klagomål.docx", "A 35775-2022")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0643/klagomålsmail/A 35775-2022 FSC-klagomål mail.docx", "A 35775-2022")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0643/tillsyn/A 35775-2022 tillsynsbegäran.docx", "A 35775-2022")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0643/tillsynsmail/A 35775-2022 tillsynsbegäran mail.docx", "A 35775-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>A 58663-2024</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
         <v>45635</v>
       </c>
-      <c r="E21" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>HABO</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
+      <c r="E22" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>HABO</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
         <v>2</v>
       </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
         <v>2</v>
       </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
         <v>2</v>
       </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
         <v>2</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T22" t="n">
         <v>2</v>
       </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Motaggsvamp
 Rhithrogena germanica</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0643/artfynd/A 58663-2024 artfynd.xlsx", "A 58663-2024")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0643/kartor/A 58663-2024 karta.png", "A 58663-2024")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0643/kartor_geotiff/A 58663-2024 georefererad karta.tif", "A 58663-2024")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0643/klagomål/A 58663-2024 FSC-klagomål.docx", "A 58663-2024")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0643/klagomålsmail/A 58663-2024 FSC-klagomål mail.docx", "A 58663-2024")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0643/tillsyn/A 58663-2024 tillsynsbegäran.docx", "A 58663-2024")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0643/tillsynsmail/A 58663-2024 tillsynsbegäran mail.docx", "A 58663-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 38067-2025</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>45882</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>JÖNKÖPINGS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>HABO</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1</v>
-      </c>
-      <c r="N22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2</v>
-      </c>
-      <c r="R22" t="n">
-        <v>2</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Cypresslummer
-Torrmusseron</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/artfynd/A 38067-2025 artfynd.xlsx", "A 38067-2025")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/kartor/A 38067-2025 karta.png", "A 38067-2025")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/kartor_geotiff/A 38067-2025 georefererad karta.tif", "A 38067-2025")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/klagomål/A 38067-2025 FSC-klagomål.docx", "A 38067-2025")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/klagomålsmail/A 38067-2025 FSC-klagomål mail.docx", "A 38067-2025")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/tillsyn/A 38067-2025 tillsynsbegäran.docx", "A 38067-2025")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/tillsynsmail/A 38067-2025 tillsynsbegäran mail.docx", "A 38067-2025")</f>
         <v/>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
         <v>45543</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>44749</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>45597</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 58668-2024</t>
+          <t>A 38055-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3270,10 +3270,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45635</v>
+        <v>45882</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3285,17 +3285,22 @@
           <t>HABO</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>1.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3310,7 +3315,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3326,35 +3331,35 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/artfynd/A 58668-2024 artfynd.xlsx", "A 58668-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/artfynd/A 38055-2025 artfynd.xlsx", "A 38055-2025")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/kartor/A 58668-2024 karta.png", "A 58668-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/kartor/A 38055-2025 karta.png", "A 38055-2025")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/kartor_geotiff/A 58668-2024 georefererad karta.tif", "A 58668-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/kartor_geotiff/A 38055-2025 georefererad karta.tif", "A 38055-2025")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/klagomål/A 58668-2024 FSC-klagomål.docx", "A 58668-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/klagomål/A 38055-2025 FSC-klagomål.docx", "A 38055-2025")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/klagomålsmail/A 58668-2024 FSC-klagomål mail.docx", "A 58668-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/klagomålsmail/A 38055-2025 FSC-klagomål mail.docx", "A 38055-2025")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/tillsyn/A 58668-2024 tillsynsbegäran.docx", "A 58668-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/tillsyn/A 38055-2025 tillsynsbegäran.docx", "A 38055-2025")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/tillsynsmail/A 58668-2024 tillsynsbegäran mail.docx", "A 58668-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/tillsynsmail/A 38055-2025 tillsynsbegäran mail.docx", "A 38055-2025")</f>
         <v/>
       </c>
     </row>
@@ -3378,7 +3383,7 @@
         <v>45933</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3466,7 +3471,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 15587-2025</t>
+          <t>A 58668-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3476,14 +3481,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45747</v>
+        <v>45635</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3496,17 +3501,17 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
         <v>1</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
@@ -3520,7 +3525,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3536,39 +3541,35 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/artfynd/A 15587-2025 artfynd.xlsx", "A 15587-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/artfynd/A 58668-2024 artfynd.xlsx", "A 58668-2024")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/kartor/A 15587-2025 karta.png", "A 15587-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/kartor/A 58668-2024 karta.png", "A 58668-2024")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/kartor_geotiff/A 15587-2025 georefererad karta.tif", "A 15587-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/kartor_geotiff/A 58668-2024 georefererad karta.tif", "A 58668-2024")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/klagomål/A 15587-2025 FSC-klagomål.docx", "A 15587-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/klagomål/A 58668-2024 FSC-klagomål.docx", "A 58668-2024")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/klagomålsmail/A 15587-2025 FSC-klagomål mail.docx", "A 15587-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/klagomålsmail/A 58668-2024 FSC-klagomål mail.docx", "A 58668-2024")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/tillsyn/A 15587-2025 tillsynsbegäran.docx", "A 15587-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/tillsyn/A 58668-2024 tillsynsbegäran.docx", "A 58668-2024")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/tillsynsmail/A 15587-2025 tillsynsbegäran mail.docx", "A 15587-2025")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/fåglar/A 15587-2025 prioriterade fågelarter.docx", "A 15587-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/tillsynsmail/A 58668-2024 tillsynsbegäran mail.docx", "A 58668-2024")</f>
         <v/>
       </c>
     </row>
@@ -3592,7 +3593,7 @@
         <v>45985</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3685,7 +3686,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 35626-2022</t>
+          <t>A 15587-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3695,14 +3696,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44799</v>
+        <v>45747</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3714,16 +3715,11 @@
           <t>HABO</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -3735,7 +3731,7 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -3744,58 +3740,62 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/artfynd/A 35626-2022 artfynd.xlsx", "A 35626-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/artfynd/A 15587-2025 artfynd.xlsx", "A 15587-2025")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/kartor/A 35626-2022 karta.png", "A 35626-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/kartor/A 15587-2025 karta.png", "A 15587-2025")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/kartor_geotiff/A 35626-2022 georefererad karta.tif", "A 35626-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/kartor_geotiff/A 15587-2025 georefererad karta.tif", "A 15587-2025")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/klagomål/A 35626-2022 FSC-klagomål.docx", "A 35626-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/klagomål/A 15587-2025 FSC-klagomål.docx", "A 15587-2025")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/klagomålsmail/A 35626-2022 FSC-klagomål mail.docx", "A 35626-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/klagomålsmail/A 15587-2025 FSC-klagomål mail.docx", "A 15587-2025")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/tillsyn/A 35626-2022 tillsynsbegäran.docx", "A 35626-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/tillsyn/A 15587-2025 tillsynsbegäran.docx", "A 15587-2025")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/tillsynsmail/A 35626-2022 tillsynsbegäran mail.docx", "A 35626-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/tillsynsmail/A 15587-2025 tillsynsbegäran mail.docx", "A 15587-2025")</f>
+        <v/>
+      </c>
+      <c r="AE30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/fåglar/A 15587-2025 prioriterade fågelarter.docx", "A 15587-2025")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 58644-2024</t>
+          <t>A 35626-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3809,10 +3809,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45635</v>
+        <v>44799</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3824,8 +3824,13 @@
           <t>HABO</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>4.5</v>
+        <v>1.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3834,13 +3839,13 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
         <v>1</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -3852,55 +3857,55 @@
         <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/artfynd/A 58644-2024 artfynd.xlsx", "A 58644-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/artfynd/A 35626-2022 artfynd.xlsx", "A 35626-2022")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/kartor/A 58644-2024 karta.png", "A 58644-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/kartor/A 35626-2022 karta.png", "A 35626-2022")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/kartor_geotiff/A 58644-2024 georefererad karta.tif", "A 58644-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/kartor_geotiff/A 35626-2022 georefererad karta.tif", "A 35626-2022")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/klagomål/A 58644-2024 FSC-klagomål.docx", "A 58644-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/klagomål/A 35626-2022 FSC-klagomål.docx", "A 35626-2022")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/klagomålsmail/A 58644-2024 FSC-klagomål mail.docx", "A 58644-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/klagomålsmail/A 35626-2022 FSC-klagomål mail.docx", "A 35626-2022")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/tillsyn/A 58644-2024 tillsynsbegäran.docx", "A 58644-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/tillsyn/A 35626-2022 tillsynsbegäran.docx", "A 35626-2022")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/tillsynsmail/A 58644-2024 tillsynsbegäran mail.docx", "A 58644-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/tillsynsmail/A 35626-2022 tillsynsbegäran mail.docx", "A 35626-2022")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 44439-2023</t>
+          <t>A 58644-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3914,10 +3919,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45183</v>
+        <v>45635</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3929,13 +3934,8 @@
           <t>HABO</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3968,49 +3968,49 @@
         <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/artfynd/A 44439-2023 artfynd.xlsx", "A 44439-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/artfynd/A 58644-2024 artfynd.xlsx", "A 58644-2024")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/kartor/A 44439-2023 karta.png", "A 44439-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/kartor/A 58644-2024 karta.png", "A 58644-2024")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/kartor_geotiff/A 44439-2023 georefererad karta.tif", "A 44439-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/kartor_geotiff/A 58644-2024 georefererad karta.tif", "A 58644-2024")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/klagomål/A 44439-2023 FSC-klagomål.docx", "A 44439-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/klagomål/A 58644-2024 FSC-klagomål.docx", "A 58644-2024")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/klagomålsmail/A 44439-2023 FSC-klagomål mail.docx", "A 44439-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/klagomålsmail/A 58644-2024 FSC-klagomål mail.docx", "A 58644-2024")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/tillsyn/A 44439-2023 tillsynsbegäran.docx", "A 44439-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/tillsyn/A 58644-2024 tillsynsbegäran.docx", "A 58644-2024")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/tillsynsmail/A 44439-2023 tillsynsbegäran mail.docx", "A 44439-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/tillsynsmail/A 58644-2024 tillsynsbegäran mail.docx", "A 58644-2024")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 27669-2025</t>
+          <t>A 44439-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4024,10 +4024,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45813</v>
+        <v>45183</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4039,11 +4039,16 @@
           <t>HABO</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>7.2</v>
+        <v>5.3</v>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -4073,49 +4078,49 @@
         <v>1</v>
       </c>
       <c r="T33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Mellanlummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/artfynd/A 27669-2025 artfynd.xlsx", "A 27669-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/artfynd/A 44439-2023 artfynd.xlsx", "A 44439-2023")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/kartor/A 27669-2025 karta.png", "A 27669-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/kartor/A 44439-2023 karta.png", "A 44439-2023")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/kartor_geotiff/A 27669-2025 georefererad karta.tif", "A 27669-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/kartor_geotiff/A 44439-2023 georefererad karta.tif", "A 44439-2023")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/klagomål/A 27669-2025 FSC-klagomål.docx", "A 27669-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/klagomål/A 44439-2023 FSC-klagomål.docx", "A 44439-2023")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/klagomålsmail/A 27669-2025 FSC-klagomål mail.docx", "A 27669-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/klagomålsmail/A 44439-2023 FSC-klagomål mail.docx", "A 44439-2023")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/tillsyn/A 27669-2025 tillsynsbegäran.docx", "A 27669-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/tillsyn/A 44439-2023 tillsynsbegäran.docx", "A 44439-2023")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/tillsynsmail/A 27669-2025 tillsynsbegäran mail.docx", "A 27669-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/tillsynsmail/A 44439-2023 tillsynsbegäran mail.docx", "A 44439-2023")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 38055-2025</t>
+          <t>A 27669-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4129,10 +4134,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45882</v>
+        <v>45813</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4144,23 +4149,18 @@
           <t>HABO</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
         <v>1</v>
       </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
       <c r="M34" t="n">
         <v>0</v>
       </c>
@@ -4174,7 +4174,7 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -4190,35 +4190,35 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mellanlummer</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/artfynd/A 38055-2025 artfynd.xlsx", "A 38055-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/artfynd/A 27669-2025 artfynd.xlsx", "A 27669-2025")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/kartor/A 38055-2025 karta.png", "A 38055-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/kartor/A 27669-2025 karta.png", "A 27669-2025")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/kartor_geotiff/A 38055-2025 georefererad karta.tif", "A 38055-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/kartor_geotiff/A 27669-2025 georefererad karta.tif", "A 27669-2025")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/klagomål/A 38055-2025 FSC-klagomål.docx", "A 38055-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/klagomål/A 27669-2025 FSC-klagomål.docx", "A 27669-2025")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/klagomålsmail/A 38055-2025 FSC-klagomål mail.docx", "A 38055-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/klagomålsmail/A 27669-2025 FSC-klagomål mail.docx", "A 27669-2025")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/tillsyn/A 38055-2025 tillsynsbegäran.docx", "A 38055-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/tillsyn/A 27669-2025 tillsynsbegäran.docx", "A 27669-2025")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0643/tillsynsmail/A 38055-2025 tillsynsbegäran mail.docx", "A 38055-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0643/tillsynsmail/A 27669-2025 tillsynsbegäran mail.docx", "A 27669-2025")</f>
         <v/>
       </c>
     </row>
@@ -4242,7 +4242,7 @@
         <v>45355</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>44847</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>44527</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44769</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>44846</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>44693</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         <v>44877</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 12592-2022</t>
+          <t>A 19570-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4792,10 +4792,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44640</v>
+        <v>44693</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4851,7 +4851,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 19570-2022</t>
+          <t>A 12592-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4865,10 +4865,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44693</v>
+        <v>44640</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4941,7 +4941,7 @@
         <v>44670</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>44859</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>44727</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         <v>44500</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>44469</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>44623</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         <v>45475</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5452,7 +5452,7 @@
         <v>45212</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 26212-2023</t>
+          <t>A 16509-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5522,10 +5522,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45091</v>
+        <v>45029</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.9</v>
+        <v>1.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5581,7 +5581,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 16509-2023</t>
+          <t>A 26212-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45029</v>
+        <v>45091</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.3</v>
+        <v>3.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5671,7 +5671,7 @@
         <v>45660</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>45641</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>45698</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>45636</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 4549-2025</t>
+          <t>A 35779-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5960,10 +5960,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45687</v>
+        <v>44801</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5976,7 +5976,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6019,7 +6019,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 49849-2024</t>
+          <t>A 4549-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6033,10 +6033,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45597</v>
+        <v>45687</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6046,11 +6046,6 @@
       <c r="G59" t="inlineStr">
         <is>
           <t>HABO</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I59" t="n">
@@ -6097,7 +6092,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 16727-2023</t>
+          <t>A 30340-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6111,10 +6106,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45030</v>
+        <v>45111</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6127,7 +6122,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6170,7 +6165,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 28685-2024</t>
+          <t>A 49849-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6184,10 +6179,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45478</v>
+        <v>45597</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6199,8 +6194,13 @@
           <t>HABO</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6243,7 +6243,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 54988-2024</t>
+          <t>A 28685-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45620</v>
+        <v>45478</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6273,7 +6273,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6316,7 +6316,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 55369-2024</t>
+          <t>A 16727-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6330,10 +6330,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45621</v>
+        <v>45030</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6389,7 +6389,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 55370-2024</t>
+          <t>A 54988-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6403,10 +6403,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45621</v>
+        <v>45620</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>11.5</v>
+        <v>1.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6462,7 +6462,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 55376-2024</t>
+          <t>A 55369-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6479,7 +6479,7 @@
         <v>45621</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6492,7 +6492,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6535,7 +6535,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 35779-2022</t>
+          <t>A 55370-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6549,10 +6549,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44801</v>
+        <v>45621</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6565,7 +6565,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.5</v>
+        <v>11.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6608,7 +6608,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 30340-2023</t>
+          <t>A 55376-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6622,10 +6622,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45111</v>
+        <v>45621</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6698,7 +6698,7 @@
         <v>44571</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>45475</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>45475</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>45120</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 35369-2023</t>
+          <t>A 50804-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6987,10 +6987,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45146</v>
+        <v>45602</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.3</v>
+        <v>0.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7046,7 +7046,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 50804-2024</t>
+          <t>A 35369-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7060,10 +7060,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45602</v>
+        <v>45146</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.4</v>
+        <v>3.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7136,7 +7136,7 @@
         <v>44783</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7197,7 +7197,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 16726-2023</t>
+          <t>A 55373-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7211,10 +7211,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45030</v>
+        <v>45621</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7227,7 +7227,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
         <v>45595</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         <v>45595</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7416,7 +7416,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 3710-2023</t>
+          <t>A 16726-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7430,10 +7430,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44951</v>
+        <v>45030</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7489,7 +7489,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 49168-2023</t>
+          <t>A 3710-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7503,10 +7503,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45210</v>
+        <v>44951</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7562,7 +7562,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 63922-2023</t>
+          <t>A 49168-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7576,10 +7576,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45278</v>
+        <v>45210</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7635,7 +7635,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 27796-2024</t>
+          <t>A 63922-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7649,10 +7649,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45475</v>
+        <v>45278</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7708,7 +7708,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 55368-2024</t>
+          <t>A 27796-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7718,14 +7718,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45621</v>
+        <v>45475</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7781,7 +7781,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 55375-2024</t>
+          <t>A 55368-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7791,14 +7791,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
         <v>45621</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7854,7 +7854,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 55373-2024</t>
+          <t>A 55375-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7871,7 +7871,7 @@
         <v>45621</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7884,7 +7884,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7944,7 +7944,7 @@
         <v>44896</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8017,7 +8017,7 @@
         <v>45597</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 41622-2024</t>
+          <t>A 35574-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8092,10 +8092,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45560</v>
+        <v>44799</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8108,7 +8108,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8151,7 +8151,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 35574-2022</t>
+          <t>A 41622-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8165,10 +8165,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44799</v>
+        <v>45560</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8241,7 +8241,7 @@
         <v>45107</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8314,7 +8314,7 @@
         <v>45121</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>45149</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>44749</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         <v>44749</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8589,7 +8589,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 26202-2023</t>
+          <t>A 16458-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8603,10 +8603,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45091</v>
+        <v>45751</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8619,7 +8619,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.2</v>
+        <v>2.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8662,7 +8662,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 58673-2024</t>
+          <t>A 30350-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8676,10 +8676,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45635</v>
+        <v>45111</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8735,7 +8735,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 61580-2024</t>
+          <t>A 26202-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8749,10 +8749,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45646</v>
+        <v>45091</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.1</v>
+        <v>0.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8808,7 +8808,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 1915-2025</t>
+          <t>A 58673-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8822,10 +8822,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45671</v>
+        <v>45635</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8838,7 +8838,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8881,7 +8881,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 28131-2023</t>
+          <t>A 37438-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8895,10 +8895,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45099</v>
+        <v>45877</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8911,7 +8911,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8954,7 +8954,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 28140-2023</t>
+          <t>A 38759-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8968,10 +8968,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45099</v>
+        <v>45887</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8984,7 +8984,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 30350-2023</t>
+          <t>A 1915-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9041,10 +9041,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45111</v>
+        <v>45671</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 26774-2024</t>
+          <t>A 28131-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9114,10 +9114,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45469</v>
+        <v>45099</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9173,7 +9173,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 38779-2022</t>
+          <t>A 28140-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9187,10 +9187,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44816</v>
+        <v>45099</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9246,7 +9246,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 45601-2022</t>
+          <t>A 19735-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9260,10 +9260,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44845</v>
+        <v>46135</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>3</v>
+        <v>0.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9319,7 +9319,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 38759-2025</t>
+          <t>A 26774-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9333,10 +9333,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45887</v>
+        <v>45469</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9392,7 +9392,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 17941-2025</t>
+          <t>A 61580-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9406,10 +9406,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45760</v>
+        <v>45646</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9422,7 +9422,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9465,7 +9465,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 54892-2021</t>
+          <t>A 38065-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9479,10 +9479,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44474</v>
+        <v>45882</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9494,8 +9494,13 @@
           <t>HABO</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>1.5</v>
+        <v>4.1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9538,7 +9543,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 28780-2025</t>
+          <t>A 38125-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9552,10 +9557,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45820</v>
+        <v>45882</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9568,7 +9573,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9611,7 +9616,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 38069-2025</t>
+          <t>A 6226-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9625,10 +9630,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45882</v>
+        <v>45698</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9640,13 +9645,8 @@
           <t>HABO</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 2780-2023</t>
+          <t>A 38122-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9703,10 +9703,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44944</v>
+        <v>45882</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9779,7 +9779,7 @@
         <v>45896</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9835,7 +9835,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 58452-2021</t>
+          <t>A 38779-2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9849,10 +9849,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44488</v>
+        <v>44816</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9865,7 +9865,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9908,7 +9908,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 41962-2025</t>
+          <t>A 45601-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9922,10 +9922,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45903</v>
+        <v>44845</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9938,7 +9938,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9981,7 +9981,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 54987-2024</t>
+          <t>A 38069-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9995,10 +9995,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45620</v>
+        <v>45882</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10010,8 +10010,13 @@
           <t>HABO</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>4.2</v>
+        <v>6.8</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10054,7 +10059,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 10943-2022</t>
+          <t>A 41962-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10068,10 +10073,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44628</v>
+        <v>45903</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10127,7 +10132,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 1876-2022</t>
+          <t>A 58452-2021</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10141,10 +10146,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44575</v>
+        <v>44488</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10157,7 +10162,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10200,7 +10205,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 15516-2023</t>
+          <t>A 28780-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10214,10 +10219,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45020</v>
+        <v>45820</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10230,7 +10235,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10273,7 +10278,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 15518-2023</t>
+          <t>A 45321-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10287,10 +10292,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45020</v>
+        <v>45922</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10303,7 +10308,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10346,7 +10351,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 57422-2023</t>
+          <t>A 17941-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10360,10 +10365,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45246</v>
+        <v>45760</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10376,7 +10381,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10419,7 +10424,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 45321-2025</t>
+          <t>A 45322-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10436,7 +10441,7 @@
         <v>45922</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10449,7 +10454,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10492,7 +10497,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 45322-2025</t>
+          <t>A 54892-2021</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10506,10 +10511,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45922</v>
+        <v>44474</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10522,7 +10527,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10565,7 +10570,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 51588-2023</t>
+          <t>A 46589-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10575,14 +10580,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45222</v>
+        <v>45926</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10595,7 +10600,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10638,7 +10643,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 40883-2023</t>
+          <t>A 47773-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10652,10 +10657,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45173</v>
+        <v>45931</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10668,7 +10673,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10711,7 +10716,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 46589-2025</t>
+          <t>A 2780-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10725,10 +10730,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45926</v>
+        <v>44944</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10741,7 +10746,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10784,7 +10789,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 40638-2024</t>
+          <t>A 57422-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10798,10 +10803,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45558</v>
+        <v>45246</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10814,7 +10819,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10857,7 +10862,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 47773-2025</t>
+          <t>A 54987-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10871,10 +10876,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45931</v>
+        <v>45620</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10887,7 +10892,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.2</v>
+        <v>4.2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10930,7 +10935,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 56767-2022</t>
+          <t>A 10943-2022</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10944,10 +10949,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44894</v>
+        <v>44628</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10960,7 +10965,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11003,7 +11008,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 26329-2024</t>
+          <t>A 1876-2022</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11017,10 +11022,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45469</v>
+        <v>44575</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11032,13 +11037,8 @@
           <t>HABO</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>4.9</v>
+        <v>1.4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11081,7 +11081,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 28813-2022</t>
+          <t>A 15516-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11095,10 +11095,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44749</v>
+        <v>45020</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11111,7 +11111,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>4.5</v>
+        <v>1.8</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11154,7 +11154,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 28816-2022</t>
+          <t>A 15518-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11168,10 +11168,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44749</v>
+        <v>45020</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>5.2</v>
+        <v>2.5</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11227,7 +11227,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 16459-2025</t>
+          <t>A 46551-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11241,10 +11241,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45751</v>
+        <v>45926</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11257,7 +11257,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11300,7 +11300,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 11075-2022</t>
+          <t>A 51447-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11314,10 +11314,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44628</v>
+        <v>45950</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11330,7 +11330,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11373,7 +11373,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 28135-2023</t>
+          <t>A 51676-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11387,10 +11387,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45099</v>
+        <v>45951</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11446,7 +11446,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 19370-2024</t>
+          <t>A 51588-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11456,14 +11456,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45429</v>
+        <v>45222</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11519,7 +11519,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 51447-2025</t>
+          <t>A 40883-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11533,10 +11533,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45950</v>
+        <v>45173</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>3.8</v>
+        <v>1.4</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11592,7 +11592,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 51676-2025</t>
+          <t>A 40638-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11606,10 +11606,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45951</v>
+        <v>45558</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11622,7 +11622,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11665,7 +11665,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 15252-2024</t>
+          <t>A 56767-2022</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11679,10 +11679,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45400</v>
+        <v>44894</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11695,7 +11695,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11738,7 +11738,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 44158-2023</t>
+          <t>A 49433-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11752,10 +11752,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45188</v>
+        <v>45595</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11768,7 +11768,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11811,7 +11811,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 23152-2024</t>
+          <t>A 55647-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11821,14 +11821,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45450</v>
+        <v>45972</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11841,7 +11841,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>3.5</v>
+        <v>0.4</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11884,7 +11884,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 49846-2024</t>
+          <t>A 56266-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11898,10 +11898,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45597</v>
+        <v>45974</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11913,13 +11913,8 @@
           <t>HABO</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11962,7 +11957,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 7754-2025</t>
+          <t>A 26329-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11976,10 +11971,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45706</v>
+        <v>45469</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11991,8 +11986,13 @@
           <t>HABO</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I140" t="n">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12035,7 +12035,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 32252-2023</t>
+          <t>A 28813-2022</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12049,10 +12049,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45120</v>
+        <v>44749</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12065,7 +12065,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12108,7 +12108,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 28690-2024</t>
+          <t>A 28816-2022</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12122,10 +12122,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45478</v>
+        <v>44749</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12138,7 +12138,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.4</v>
+        <v>5.2</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12181,7 +12181,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 55647-2025</t>
+          <t>A 58527-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12191,14 +12191,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45972</v>
+        <v>45985</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12210,8 +12210,13 @@
           <t>HABO</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I143" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12254,7 +12259,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 56266-2025</t>
+          <t>A 58528-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12268,10 +12273,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45974</v>
+        <v>45985</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12283,8 +12288,13 @@
           <t>HABO</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I144" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12327,7 +12337,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 15517-2023</t>
+          <t>A 60583-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12337,14 +12347,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45020</v>
+        <v>45996</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12357,7 +12367,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.3</v>
+        <v>4.7</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12400,7 +12410,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 6230-2025</t>
+          <t>A 58158-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12414,10 +12424,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45698</v>
+        <v>45982</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12430,7 +12440,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.3</v>
+        <v>3.7</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12473,7 +12483,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 6233-2025</t>
+          <t>A 60583-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12483,14 +12493,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45698</v>
+        <v>45996</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12503,7 +12513,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.4</v>
+        <v>4.7</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12546,7 +12556,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 46551-2025</t>
+          <t>A 16459-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12560,10 +12570,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45926</v>
+        <v>45751</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12576,7 +12586,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12619,7 +12629,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 58527-2025</t>
+          <t>A 11075-2022</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12633,10 +12643,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45985</v>
+        <v>44628</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12648,13 +12658,8 @@
           <t>HABO</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I149" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12697,7 +12702,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 58528-2025</t>
+          <t>A 28135-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12711,10 +12716,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45985</v>
+        <v>45099</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12726,13 +12731,8 @@
           <t>HABO</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I150" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12775,7 +12775,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 58158-2025</t>
+          <t>A 19370-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12789,10 +12789,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45982</v>
+        <v>45429</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12805,7 +12805,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>3.7</v>
+        <v>1.9</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12848,7 +12848,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 35148-2022</t>
+          <t>A 15252-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12862,10 +12862,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44797</v>
+        <v>45400</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12878,7 +12878,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12921,7 +12921,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 60726-2022</t>
+          <t>A 44158-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12935,10 +12935,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44913</v>
+        <v>45188</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12951,7 +12951,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12994,7 +12994,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 65067-2023</t>
+          <t>A 24606-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13008,10 +13008,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45287</v>
+        <v>46171</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13024,7 +13024,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13067,7 +13067,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 17845-2024</t>
+          <t>A 23152-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13081,10 +13081,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45419</v>
+        <v>45450</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13097,7 +13097,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13140,7 +13140,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 54288-2024</t>
+          <t>A 49846-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13154,10 +13154,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45617</v>
+        <v>45597</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13169,8 +13169,13 @@
           <t>HABO</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I156" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13213,7 +13218,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 16149-2025</t>
+          <t>A 7754-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13227,10 +13232,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45750</v>
+        <v>45706</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13243,7 +13248,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13286,7 +13291,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 62745-2023</t>
+          <t>A 61275-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13300,10 +13305,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45271</v>
+        <v>46000</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13316,7 +13321,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>3.8</v>
+        <v>0.3</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13359,7 +13364,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 59440-2024</t>
+          <t>A 61269-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13373,10 +13378,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45638</v>
+        <v>46000</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13389,7 +13394,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13432,7 +13437,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 49433-2024</t>
+          <t>A 61271-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13446,10 +13451,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45595</v>
+        <v>46000</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13462,7 +13467,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>5</v>
+        <v>0.8</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13505,7 +13510,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 61275-2025</t>
+          <t>A 61273-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13522,7 +13527,7 @@
         <v>46000</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13535,7 +13540,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.3</v>
+        <v>2.2</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13578,7 +13583,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 61269-2025</t>
+          <t>A 32252-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13592,10 +13597,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46000</v>
+        <v>45120</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13608,7 +13613,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13651,7 +13656,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 61271-2025</t>
+          <t>A 25353-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13661,14 +13666,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46000</v>
+        <v>46176</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13681,7 +13686,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13724,7 +13729,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 61273-2025</t>
+          <t>A 28690-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13738,10 +13743,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46000</v>
+        <v>45478</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13754,7 +13759,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13797,7 +13802,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 23148-2024</t>
+          <t>A 15517-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13811,10 +13816,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45450</v>
+        <v>45020</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13827,7 +13832,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13870,7 +13875,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 23153-2024</t>
+          <t>A 6230-2025</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13884,10 +13889,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45450</v>
+        <v>45698</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13900,7 +13905,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13943,7 +13948,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 45277-2024</t>
+          <t>A 6233-2025</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13957,10 +13962,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45576</v>
+        <v>45698</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13973,7 +13978,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14016,7 +14021,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 43160-2023</t>
+          <t>A 35148-2022</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14030,10 +14035,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45183</v>
+        <v>44797</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14046,7 +14051,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14089,7 +14094,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 60583-2025</t>
+          <t>A 2690-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14099,14 +14104,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45996</v>
+        <v>46037</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14119,7 +14124,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>4.7</v>
+        <v>0.3</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14162,7 +14167,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 60583-2025</t>
+          <t>A 2693-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14172,14 +14177,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45996</v>
+        <v>46037</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14192,7 +14197,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>4.7</v>
+        <v>0.5</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14235,7 +14240,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 62764-2023</t>
+          <t>A 60726-2022</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14249,10 +14254,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45271</v>
+        <v>44913</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14265,7 +14270,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14308,7 +14313,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 53264-2022</t>
+          <t>A 2681-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14322,10 +14327,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44876</v>
+        <v>46037</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14338,7 +14343,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14381,7 +14386,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 56289-2023</t>
+          <t>A 3282-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14395,10 +14400,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45242</v>
+        <v>46041</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14410,13 +14415,8 @@
           <t>HABO</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I173" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 41910-2022</t>
+          <t>A 65067-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14473,10 +14473,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44830</v>
+        <v>45287</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14489,7 +14489,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>7.6</v>
+        <v>2.1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14532,7 +14532,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 24606-2026</t>
+          <t>A 3775-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14546,10 +14546,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46171</v>
+        <v>46043</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14562,7 +14562,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14605,7 +14605,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 2861-2025</t>
+          <t>A 3792-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14619,10 +14619,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45677</v>
+        <v>46043</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14635,7 +14635,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14678,7 +14678,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 51027-2023</t>
+          <t>A 3794-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14692,10 +14692,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45218</v>
+        <v>46043</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14708,7 +14708,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14751,7 +14751,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 2690-2026</t>
+          <t>A 3783-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14765,10 +14765,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46037</v>
+        <v>46043</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14781,7 +14781,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.3</v>
+        <v>4.1</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14824,7 +14824,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 2693-2026</t>
+          <t>A 17845-2024</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14838,10 +14838,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46037</v>
+        <v>45419</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14897,7 +14897,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 47532-2023</t>
+          <t>A 3787-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14911,10 +14911,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45203</v>
+        <v>46043</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14927,7 +14927,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14970,7 +14970,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 2681-2026</t>
+          <t>A 3778-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14984,10 +14984,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46037</v>
+        <v>46043</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15043,7 +15043,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 3282-2026</t>
+          <t>A 54288-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15057,10 +15057,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46041</v>
+        <v>45617</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15073,7 +15073,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15116,7 +15116,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 59433-2024</t>
+          <t>A 27841-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15130,10 +15130,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45638</v>
+        <v>46191</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15146,7 +15146,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>10.4</v>
+        <v>2.7</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15189,7 +15189,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 3775-2026</t>
+          <t>A 27852-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15203,10 +15203,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46043</v>
+        <v>46191</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15262,7 +15262,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 3792-2026</t>
+          <t>A 27838-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15276,10 +15276,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46043</v>
+        <v>46191</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15292,7 +15292,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15335,7 +15335,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 3794-2026</t>
+          <t>A 16149-2025</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15349,10 +15349,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46043</v>
+        <v>45750</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15365,7 +15365,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15408,7 +15408,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 3783-2026</t>
+          <t>A 27858-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15422,10 +15422,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46043</v>
+        <v>46191</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15438,7 +15438,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>4.1</v>
+        <v>1.2</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15481,7 +15481,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 3787-2026</t>
+          <t>A 62745-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15495,10 +15495,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46043</v>
+        <v>45271</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15511,7 +15511,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15554,7 +15554,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 3778-2026</t>
+          <t>A 5961-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15568,10 +15568,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46043</v>
+        <v>46052</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15584,7 +15584,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15627,7 +15627,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 12606-2025</t>
+          <t>A 59440-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15641,10 +15641,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45733</v>
+        <v>45638</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15700,7 +15700,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 48894-2024</t>
+          <t>A 7419-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15714,10 +15714,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45594</v>
+        <v>46059</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15730,7 +15730,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15773,7 +15773,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 25353-2026</t>
+          <t>A 9016-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15783,14 +15783,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46176</v>
+        <v>46069</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15803,7 +15803,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15846,7 +15846,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 5961-2026</t>
+          <t>A 23148-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15860,10 +15860,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46052</v>
+        <v>45450</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15876,7 +15876,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15919,7 +15919,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 49447-2024</t>
+          <t>A 23153-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15933,10 +15933,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45595</v>
+        <v>45450</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15949,7 +15949,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15992,7 +15992,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 26711-2024</t>
+          <t>A 45277-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16006,10 +16006,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45470</v>
+        <v>45576</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16022,7 +16022,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16065,7 +16065,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 54989-2024</t>
+          <t>A 43160-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16079,10 +16079,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45620</v>
+        <v>45183</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16095,7 +16095,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16138,7 +16138,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 54990-2024</t>
+          <t>A 62764-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16152,10 +16152,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45620</v>
+        <v>45271</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16168,7 +16168,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16211,7 +16211,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 7419-2026</t>
+          <t>A 53264-2022</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16225,10 +16225,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46059</v>
+        <v>44876</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16241,7 +16241,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16284,7 +16284,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 23145-2024</t>
+          <t>A 56289-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16298,10 +16298,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45450</v>
+        <v>45242</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16313,8 +16313,13 @@
           <t>HABO</t>
         </is>
       </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I199" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16357,7 +16362,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 23156-2024</t>
+          <t>A 41910-2022</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16371,10 +16376,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45450</v>
+        <v>44830</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16387,7 +16392,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16430,7 +16435,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 9016-2026</t>
+          <t>A 29496-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16444,10 +16449,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46069</v>
+        <v>46203</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16460,7 +16465,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>6</v>
+        <v>0.9</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16503,7 +16508,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 15251-2024</t>
+          <t>A 29492-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16517,10 +16522,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45400</v>
+        <v>46203</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16533,7 +16538,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16576,7 +16581,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 12999-2025</t>
+          <t>A 2861-2025</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16590,10 +16595,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45734</v>
+        <v>45677</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16606,7 +16611,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16649,7 +16654,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 30863-2023</t>
+          <t>A 51027-2023</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16663,10 +16668,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45113</v>
+        <v>45218</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16679,7 +16684,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16722,7 +16727,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 40280-2024</t>
+          <t>A 33307-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16732,14 +16737,14 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45554</v>
+        <v>46246</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16752,7 +16757,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>6.9</v>
+        <v>4.2</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16795,7 +16800,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 54693-2023</t>
+          <t>A 47532-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16809,10 +16814,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45236</v>
+        <v>45203</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16825,7 +16830,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>5.3</v>
+        <v>2.5</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16868,7 +16873,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 51444-2023</t>
+          <t>A 59433-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16882,10 +16887,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45220</v>
+        <v>45638</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16898,7 +16903,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>2.5</v>
+        <v>10.4</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16941,7 +16946,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 27841-2026</t>
+          <t>A 29335-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16955,10 +16960,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46191</v>
+        <v>46202</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16971,7 +16976,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -17014,7 +17019,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 27852-2026</t>
+          <t>A 12606-2025</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -17028,10 +17033,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46191</v>
+        <v>45733</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17044,7 +17049,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -17087,7 +17092,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 27838-2026</t>
+          <t>A 48894-2024</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17101,10 +17106,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46191</v>
+        <v>45594</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17117,7 +17122,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17160,7 +17165,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 27858-2026</t>
+          <t>A 33317-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17174,10 +17179,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46191</v>
+        <v>46246</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17190,7 +17195,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17233,7 +17238,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 8849-2024</t>
+          <t>A 49447-2024</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17247,10 +17252,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45356</v>
+        <v>45595</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17263,7 +17268,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17306,7 +17311,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 2073-2023</t>
+          <t>A 26711-2024</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17320,10 +17325,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>44939</v>
+        <v>45470</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17336,7 +17341,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>4.3</v>
+        <v>0.6</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17379,7 +17384,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 11906-2023</t>
+          <t>A 54989-2024</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17393,10 +17398,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>44995</v>
+        <v>45620</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17409,7 +17414,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>3.9</v>
+        <v>2.1</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17452,7 +17457,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 26207-2023</t>
+          <t>A 54990-2024</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17466,10 +17471,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45091</v>
+        <v>45620</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17482,7 +17487,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17525,7 +17530,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 53300-2022</t>
+          <t>A 23145-2024</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17539,10 +17544,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>44877</v>
+        <v>45450</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17555,7 +17560,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17598,7 +17603,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 14724-2024</t>
+          <t>A 23156-2024</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17612,10 +17617,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45397</v>
+        <v>45450</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17628,7 +17633,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>1</v>
+        <v>7.5</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17671,7 +17676,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 1699-2024</t>
+          <t>A 15251-2024</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17685,10 +17690,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45307</v>
+        <v>45400</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17701,7 +17706,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17744,7 +17749,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 46062-2024</t>
+          <t>A 33738-2026</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17758,10 +17763,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45580</v>
+        <v>46251</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17774,7 +17779,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17817,7 +17822,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 13880-2023</t>
+          <t>A 12999-2025</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17831,10 +17836,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45007</v>
+        <v>45734</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17847,7 +17852,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17890,7 +17895,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 36483-2023</t>
+          <t>A 30863-2023</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17904,10 +17909,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45152</v>
+        <v>45113</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17920,7 +17925,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17963,7 +17968,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 31909-2024</t>
+          <t>A 40280-2024</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17973,14 +17978,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45510</v>
+        <v>45554</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17993,7 +17998,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>1.3</v>
+        <v>6.9</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -18036,7 +18041,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 29496-2026</t>
+          <t>A 3077-2024</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -18050,10 +18055,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>46203</v>
+        <v>45316</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18066,7 +18071,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -18109,7 +18114,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 45275-2024</t>
+          <t>A 54693-2023</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -18123,10 +18128,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45576</v>
+        <v>45236</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18139,7 +18144,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>0.4</v>
+        <v>5.3</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -18182,7 +18187,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 58666-2024</t>
+          <t>A 48893-2024</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18196,10 +18201,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45635</v>
+        <v>45594</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18212,7 +18217,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18255,7 +18260,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 29492-2026</t>
+          <t>A 51444-2023</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18269,10 +18274,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>46203</v>
+        <v>45220</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18285,7 +18290,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18328,7 +18333,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 33307-2026</t>
+          <t>A 34479-2026</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18342,10 +18347,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18358,7 +18363,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>4.2</v>
+        <v>1.9</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18401,7 +18406,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 17519-2025</t>
+          <t>A 8849-2024</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18415,10 +18420,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45757</v>
+        <v>45356</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18431,7 +18436,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18474,7 +18479,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 17520-2025</t>
+          <t>A 31098-2026</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18488,10 +18493,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45757</v>
+        <v>46216</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18504,7 +18509,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18547,7 +18552,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 19735-2026</t>
+          <t>A 2073-2023</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18561,10 +18566,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>46135</v>
+        <v>44939</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18577,7 +18582,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>0.3</v>
+        <v>4.3</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18620,7 +18625,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 6226-2025</t>
+          <t>A 11906-2023</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18634,10 +18639,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45698</v>
+        <v>44995</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18650,7 +18655,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>6</v>
+        <v>3.9</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18693,7 +18698,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 47836-2023</t>
+          <t>A 26207-2023</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18707,10 +18712,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45204</v>
+        <v>45091</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18723,7 +18728,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18766,7 +18771,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 49448-2024</t>
+          <t>A 53300-2022</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18780,10 +18785,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45595</v>
+        <v>44877</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18796,7 +18801,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18839,7 +18844,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 13850-2024</t>
+          <t>A 14724-2024</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18853,10 +18858,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45390</v>
+        <v>45397</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18869,7 +18874,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>4.6</v>
+        <v>1</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18912,7 +18917,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 29335-2026</t>
+          <t>A 1699-2024</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18926,10 +18931,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>46202</v>
+        <v>45307</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18985,7 +18990,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 33317-2026</t>
+          <t>A 46062-2024</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18999,10 +19004,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>46246</v>
+        <v>45580</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19015,7 +19020,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -19058,7 +19063,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 57999-2024</t>
+          <t>A 13880-2023</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -19072,10 +19077,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45631</v>
+        <v>45007</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19088,7 +19093,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -19131,7 +19136,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 59928-2022</t>
+          <t>A 36483-2023</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -19145,10 +19150,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>44909</v>
+        <v>45152</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19161,7 +19166,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -19204,7 +19209,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 11426-2024</t>
+          <t>A 31909-2024</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -19218,10 +19223,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45372</v>
+        <v>45510</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19234,7 +19239,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -19277,7 +19282,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 61665-2024</t>
+          <t>A 36029-2026</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -19291,10 +19296,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45647</v>
+        <v>46267</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19307,7 +19312,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -19350,7 +19355,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 58430-2021</t>
+          <t>A 45275-2024</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -19364,10 +19369,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>44488</v>
+        <v>45576</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19380,7 +19385,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -19423,7 +19428,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 33738-2026</t>
+          <t>A 58666-2024</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19437,10 +19442,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>46251</v>
+        <v>45635</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19453,7 +19458,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -19496,7 +19501,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 59057-2024</t>
+          <t>A 36030-2026</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19510,10 +19515,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45636</v>
+        <v>46267</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19526,7 +19531,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>1.7</v>
+        <v>17.7</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19569,7 +19574,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 3077-2024</t>
+          <t>A 36230-2026</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19579,14 +19584,14 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>45316</v>
+        <v>46268</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19599,7 +19604,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19642,7 +19647,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 33030-2026</t>
+          <t>A 17519-2025</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19656,10 +19661,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>46244</v>
+        <v>45757</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19672,7 +19677,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>4.2</v>
+        <v>0.6</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19715,7 +19720,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 48893-2024</t>
+          <t>A 17520-2025</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19729,10 +19734,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45594</v>
+        <v>45757</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19745,7 +19750,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19788,7 +19793,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 60679-2024</t>
+          <t>A 36411-2026</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19802,10 +19807,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45644</v>
+        <v>46268</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19818,7 +19823,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>1</v>
+        <v>10.5</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19861,7 +19866,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 32329-2023</t>
+          <t>A 36239-2026</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19875,10 +19880,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>45120</v>
+        <v>46268</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19891,7 +19896,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>4.8</v>
+        <v>1.4</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19934,7 +19939,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 34479-2026</t>
+          <t>A 47836-2023</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19948,10 +19953,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>46254</v>
+        <v>45204</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19964,7 +19969,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>1.9</v>
+        <v>4.8</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -20007,7 +20012,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 32235-2023</t>
+          <t>A 49448-2024</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -20021,10 +20026,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>45119</v>
+        <v>45595</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20037,7 +20042,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>7.1</v>
+        <v>2</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -20080,7 +20085,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 32236-2023</t>
+          <t>A 36914-2026</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -20094,10 +20099,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>45119</v>
+        <v>46273</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20109,8 +20114,13 @@
           <t>HABO</t>
         </is>
       </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I251" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -20153,7 +20163,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 58452-2021</t>
+          <t>A 13850-2024</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -20167,10 +20177,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>44488</v>
+        <v>45390</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20183,7 +20193,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>2.1</v>
+        <v>4.6</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -20226,7 +20236,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 58458-2021</t>
+          <t>A 36916-2026</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -20240,10 +20250,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>44488</v>
+        <v>46273</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20255,8 +20265,13 @@
           <t>HABO</t>
         </is>
       </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I253" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -20299,7 +20314,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 31098-2026</t>
+          <t>A 57999-2024</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -20313,10 +20328,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>46216</v>
+        <v>45631</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20329,7 +20344,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -20372,7 +20387,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 32238-2023</t>
+          <t>A 59928-2022</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -20386,10 +20401,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>45119</v>
+        <v>44909</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20402,7 +20417,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -20445,7 +20460,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 36481-2023</t>
+          <t>A 11426-2024</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -20459,10 +20474,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>45152</v>
+        <v>45372</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20475,7 +20490,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>5.3</v>
+        <v>2.3</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -20518,7 +20533,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 11887-2023</t>
+          <t>A 31959-2026</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -20532,10 +20547,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>44995</v>
+        <v>46232</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20548,7 +20563,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -20591,7 +20606,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 9931-2024</t>
+          <t>A 61665-2024</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -20605,10 +20620,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>45363</v>
+        <v>45647</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20621,7 +20636,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -20664,7 +20679,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 60971-2022</t>
+          <t>A 58430-2021</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20678,10 +20693,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>44914</v>
+        <v>44488</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20694,7 +20709,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -20737,7 +20752,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 50710-2023</t>
+          <t>A 59057-2024</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -20751,10 +20766,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>45217</v>
+        <v>45636</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20767,7 +20782,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -20810,7 +20825,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 29408-2023</t>
+          <t>A 60679-2024</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -20824,10 +20839,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>45106</v>
+        <v>45644</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20840,7 +20855,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -20883,7 +20898,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 32245-2023</t>
+          <t>A 32329-2023</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -20897,10 +20912,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>45119</v>
+        <v>45120</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20913,7 +20928,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>0.7</v>
+        <v>4.8</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -20956,7 +20971,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 32246-2023</t>
+          <t>A 32235-2023</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -20970,10 +20985,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>45120</v>
+        <v>45119</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20986,7 +21001,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>0.6</v>
+        <v>7.1</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -21029,7 +21044,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>A 32247-2023</t>
+          <t>A 32236-2023</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -21043,10 +21058,10 @@
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>45120</v>
+        <v>45119</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21059,7 +21074,7 @@
         </is>
       </c>
       <c r="I264" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -21102,7 +21117,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>A 32253-2023</t>
+          <t>A 58452-2021</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -21116,10 +21131,10 @@
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>45120</v>
+        <v>44488</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21132,7 +21147,7 @@
         </is>
       </c>
       <c r="I265" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -21175,7 +21190,7 @@
     <row r="266" ht="15" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>A 4551-2025</t>
+          <t>A 58458-2021</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -21189,10 +21204,10 @@
         </is>
       </c>
       <c r="D266" s="1" t="n">
-        <v>45687</v>
+        <v>44488</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21205,7 +21220,7 @@
         </is>
       </c>
       <c r="I266" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -21248,7 +21263,7 @@
     <row r="267" ht="15" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>A 31591-2022</t>
+          <t>A 32238-2023</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -21262,10 +21277,10 @@
         </is>
       </c>
       <c r="D267" s="1" t="n">
-        <v>44775</v>
+        <v>45119</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21278,7 +21293,7 @@
         </is>
       </c>
       <c r="I267" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -21321,7 +21336,7 @@
     <row r="268" ht="15" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>A 36029-2026</t>
+          <t>A 36481-2023</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -21335,10 +21350,10 @@
         </is>
       </c>
       <c r="D268" s="1" t="n">
-        <v>46267</v>
+        <v>45152</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21351,7 +21366,7 @@
         </is>
       </c>
       <c r="I268" t="n">
-        <v>2.9</v>
+        <v>5.3</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
@@ -21394,7 +21409,7 @@
     <row r="269" ht="15" customHeight="1">
       <c r="A269" t="inlineStr">
         <is>
-          <t>A 36030-2026</t>
+          <t>A 33030-2026</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -21408,10 +21423,10 @@
         </is>
       </c>
       <c r="D269" s="1" t="n">
-        <v>46267</v>
+        <v>46244</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21424,7 +21439,7 @@
         </is>
       </c>
       <c r="I269" t="n">
-        <v>17.7</v>
+        <v>4.2</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
@@ -21467,7 +21482,7 @@
     <row r="270" ht="15" customHeight="1">
       <c r="A270" t="inlineStr">
         <is>
-          <t>A 36230-2026</t>
+          <t>A 11887-2023</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -21477,14 +21492,14 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D270" s="1" t="n">
-        <v>46268</v>
+        <v>44995</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21497,7 +21512,7 @@
         </is>
       </c>
       <c r="I270" t="n">
-        <v>5</v>
+        <v>1.3</v>
       </c>
       <c r="J270" t="n">
         <v>0</v>
@@ -21540,7 +21555,7 @@
     <row r="271" ht="15" customHeight="1">
       <c r="A271" t="inlineStr">
         <is>
-          <t>A 36411-2026</t>
+          <t>A 9931-2024</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -21554,10 +21569,10 @@
         </is>
       </c>
       <c r="D271" s="1" t="n">
-        <v>46268</v>
+        <v>45363</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21570,7 +21585,7 @@
         </is>
       </c>
       <c r="I271" t="n">
-        <v>10.5</v>
+        <v>1.1</v>
       </c>
       <c r="J271" t="n">
         <v>0</v>
@@ -21613,7 +21628,7 @@
     <row r="272" ht="15" customHeight="1">
       <c r="A272" t="inlineStr">
         <is>
-          <t>A 21072-2025</t>
+          <t>A 60971-2022</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -21627,10 +21642,10 @@
         </is>
       </c>
       <c r="D272" s="1" t="n">
-        <v>45777</v>
+        <v>44914</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21643,7 +21658,7 @@
         </is>
       </c>
       <c r="I272" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J272" t="n">
         <v>0</v>
@@ -21686,7 +21701,7 @@
     <row r="273" ht="15" customHeight="1">
       <c r="A273" t="inlineStr">
         <is>
-          <t>A 21073-2025</t>
+          <t>A 50710-2023</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -21700,10 +21715,10 @@
         </is>
       </c>
       <c r="D273" s="1" t="n">
-        <v>45777</v>
+        <v>45217</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21716,7 +21731,7 @@
         </is>
       </c>
       <c r="I273" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J273" t="n">
         <v>0</v>
@@ -21759,7 +21774,7 @@
     <row r="274" ht="15" customHeight="1">
       <c r="A274" t="inlineStr">
         <is>
-          <t>A 36239-2026</t>
+          <t>A 29408-2023</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -21773,10 +21788,10 @@
         </is>
       </c>
       <c r="D274" s="1" t="n">
-        <v>46268</v>
+        <v>45106</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21789,7 +21804,7 @@
         </is>
       </c>
       <c r="I274" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J274" t="n">
         <v>0</v>
@@ -21832,7 +21847,7 @@
     <row r="275" ht="15" customHeight="1">
       <c r="A275" t="inlineStr">
         <is>
-          <t>A 36914-2026</t>
+          <t>A 32245-2023</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -21846,10 +21861,10 @@
         </is>
       </c>
       <c r="D275" s="1" t="n">
-        <v>46273</v>
+        <v>45119</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21861,13 +21876,8 @@
           <t>HABO</t>
         </is>
       </c>
-      <c r="H275" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I275" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J275" t="n">
         <v>0</v>
@@ -21910,7 +21920,7 @@
     <row r="276" ht="15" customHeight="1">
       <c r="A276" t="inlineStr">
         <is>
-          <t>A 36916-2026</t>
+          <t>A 32246-2023</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -21924,10 +21934,10 @@
         </is>
       </c>
       <c r="D276" s="1" t="n">
-        <v>46273</v>
+        <v>45120</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21937,11 +21947,6 @@
       <c r="G276" t="inlineStr">
         <is>
           <t>HABO</t>
-        </is>
-      </c>
-      <c r="H276" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I276" t="n">
@@ -21988,7 +21993,7 @@
     <row r="277" ht="15" customHeight="1">
       <c r="A277" t="inlineStr">
         <is>
-          <t>A 31959-2026</t>
+          <t>A 32247-2023</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -22002,10 +22007,10 @@
         </is>
       </c>
       <c r="D277" s="1" t="n">
-        <v>46232</v>
+        <v>45120</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22018,7 +22023,7 @@
         </is>
       </c>
       <c r="I277" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J277" t="n">
         <v>0</v>
@@ -22061,7 +22066,7 @@
     <row r="278" ht="15" customHeight="1">
       <c r="A278" t="inlineStr">
         <is>
-          <t>A 22691-2025</t>
+          <t>A 32253-2023</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -22075,10 +22080,10 @@
         </is>
       </c>
       <c r="D278" s="1" t="n">
-        <v>45789</v>
+        <v>45120</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22091,7 +22096,7 @@
         </is>
       </c>
       <c r="I278" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="J278" t="n">
         <v>0</v>
@@ -22134,7 +22139,7 @@
     <row r="279" ht="15" customHeight="1">
       <c r="A279" t="inlineStr">
         <is>
-          <t>A 52055-2024</t>
+          <t>A 4551-2025</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -22144,14 +22149,14 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D279" s="1" t="n">
-        <v>45608</v>
+        <v>45687</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22164,7 +22169,7 @@
         </is>
       </c>
       <c r="I279" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J279" t="n">
         <v>0</v>
@@ -22207,7 +22212,7 @@
     <row r="280" ht="15" customHeight="1">
       <c r="A280" t="inlineStr">
         <is>
-          <t>A 10167-2024</t>
+          <t>A 31591-2022</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -22221,10 +22226,10 @@
         </is>
       </c>
       <c r="D280" s="1" t="n">
-        <v>45364</v>
+        <v>44775</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22237,7 +22242,7 @@
         </is>
       </c>
       <c r="I280" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J280" t="n">
         <v>0</v>
@@ -22280,7 +22285,7 @@
     <row r="281" ht="15" customHeight="1">
       <c r="A281" t="inlineStr">
         <is>
-          <t>A 15802-2023</t>
+          <t>A 21072-2025</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -22294,10 +22299,10 @@
         </is>
       </c>
       <c r="D281" s="1" t="n">
-        <v>45021</v>
+        <v>45777</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22310,7 +22315,7 @@
         </is>
       </c>
       <c r="I281" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J281" t="n">
         <v>0</v>
@@ -22353,7 +22358,7 @@
     <row r="282" ht="15" customHeight="1">
       <c r="A282" t="inlineStr">
         <is>
-          <t>A 12991-2025</t>
+          <t>A 21073-2025</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -22367,10 +22372,10 @@
         </is>
       </c>
       <c r="D282" s="1" t="n">
-        <v>45734</v>
+        <v>45777</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22383,7 +22388,7 @@
         </is>
       </c>
       <c r="I282" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J282" t="n">
         <v>0</v>
@@ -22426,7 +22431,7 @@
     <row r="283" ht="15" customHeight="1">
       <c r="A283" t="inlineStr">
         <is>
-          <t>A 26519-2025</t>
+          <t>A 22691-2025</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -22440,10 +22445,10 @@
         </is>
       </c>
       <c r="D283" s="1" t="n">
-        <v>45807</v>
+        <v>45789</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22456,7 +22461,7 @@
         </is>
       </c>
       <c r="I283" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J283" t="n">
         <v>0</v>
@@ -22499,7 +22504,7 @@
     <row r="284" ht="15" customHeight="1">
       <c r="A284" t="inlineStr">
         <is>
-          <t>A 26881-2025</t>
+          <t>A 52055-2024</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -22509,14 +22514,14 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D284" s="1" t="n">
-        <v>45810</v>
+        <v>45608</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22529,7 +22534,7 @@
         </is>
       </c>
       <c r="I284" t="n">
-        <v>11.6</v>
+        <v>1.1</v>
       </c>
       <c r="J284" t="n">
         <v>0</v>
@@ -22572,7 +22577,7 @@
     <row r="285" ht="15" customHeight="1">
       <c r="A285" t="inlineStr">
         <is>
-          <t>A 27327-2025</t>
+          <t>A 10167-2024</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -22586,10 +22591,10 @@
         </is>
       </c>
       <c r="D285" s="1" t="n">
-        <v>45812</v>
+        <v>45364</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22602,7 +22607,7 @@
         </is>
       </c>
       <c r="I285" t="n">
-        <v>7.1</v>
+        <v>1.3</v>
       </c>
       <c r="J285" t="n">
         <v>0</v>
@@ -22645,7 +22650,7 @@
     <row r="286" ht="15" customHeight="1">
       <c r="A286" t="inlineStr">
         <is>
-          <t>A 26932-2025</t>
+          <t>A 15802-2023</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -22655,14 +22660,14 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D286" s="1" t="n">
-        <v>45811</v>
+        <v>45021</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22675,7 +22680,7 @@
         </is>
       </c>
       <c r="I286" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J286" t="n">
         <v>0</v>
@@ -22718,7 +22723,7 @@
     <row r="287" ht="15" customHeight="1">
       <c r="A287" t="inlineStr">
         <is>
-          <t>A 30274-2025</t>
+          <t>A 12991-2025</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -22732,10 +22737,10 @@
         </is>
       </c>
       <c r="D287" s="1" t="n">
-        <v>45827</v>
+        <v>45734</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22748,7 +22753,7 @@
         </is>
       </c>
       <c r="I287" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J287" t="n">
         <v>0</v>
@@ -22791,7 +22796,7 @@
     <row r="288" ht="15" customHeight="1">
       <c r="A288" t="inlineStr">
         <is>
-          <t>A 30272-2025</t>
+          <t>A 26519-2025</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -22805,10 +22810,10 @@
         </is>
       </c>
       <c r="D288" s="1" t="n">
-        <v>45827</v>
+        <v>45807</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22821,7 +22826,7 @@
         </is>
       </c>
       <c r="I288" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J288" t="n">
         <v>0</v>
@@ -22864,7 +22869,7 @@
     <row r="289" ht="15" customHeight="1">
       <c r="A289" t="inlineStr">
         <is>
-          <t>A 34452-2025</t>
+          <t>A 26881-2025</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -22878,10 +22883,10 @@
         </is>
       </c>
       <c r="D289" s="1" t="n">
-        <v>45846</v>
+        <v>45810</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22894,7 +22899,7 @@
         </is>
       </c>
       <c r="I289" t="n">
-        <v>0.9</v>
+        <v>11.6</v>
       </c>
       <c r="J289" t="n">
         <v>0</v>
@@ -22937,7 +22942,7 @@
     <row r="290" ht="15" customHeight="1">
       <c r="A290" t="inlineStr">
         <is>
-          <t>A 26882-2025</t>
+          <t>A 27327-2025</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -22951,10 +22956,10 @@
         </is>
       </c>
       <c r="D290" s="1" t="n">
-        <v>45810</v>
+        <v>45812</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22967,7 +22972,7 @@
         </is>
       </c>
       <c r="I290" t="n">
-        <v>4.2</v>
+        <v>7.1</v>
       </c>
       <c r="J290" t="n">
         <v>0</v>
@@ -23010,7 +23015,7 @@
     <row r="291" ht="15" customHeight="1">
       <c r="A291" t="inlineStr">
         <is>
-          <t>A 16458-2025</t>
+          <t>A 26932-2025</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -23020,14 +23025,14 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D291" s="1" t="n">
-        <v>45751</v>
+        <v>45811</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23040,7 +23045,7 @@
         </is>
       </c>
       <c r="I291" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J291" t="n">
         <v>0</v>
@@ -23083,7 +23088,7 @@
     <row r="292" ht="15" customHeight="1">
       <c r="A292" t="inlineStr">
         <is>
-          <t>A 37438-2025</t>
+          <t>A 30274-2025</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -23097,10 +23102,10 @@
         </is>
       </c>
       <c r="D292" s="1" t="n">
-        <v>45877</v>
+        <v>45827</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23113,7 +23118,7 @@
         </is>
       </c>
       <c r="I292" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J292" t="n">
         <v>0</v>
@@ -23156,7 +23161,7 @@
     <row r="293" ht="15" customHeight="1">
       <c r="A293" t="inlineStr">
         <is>
-          <t>A 38065-2025</t>
+          <t>A 30272-2025</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -23170,10 +23175,10 @@
         </is>
       </c>
       <c r="D293" s="1" t="n">
-        <v>45882</v>
+        <v>45827</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23185,13 +23190,8 @@
           <t>HABO</t>
         </is>
       </c>
-      <c r="H293" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I293" t="n">
-        <v>4.1</v>
+        <v>0.9</v>
       </c>
       <c r="J293" t="n">
         <v>0</v>
@@ -23234,7 +23234,7 @@
     <row r="294" ht="15" customHeight="1">
       <c r="A294" t="inlineStr">
         <is>
-          <t>A 38125-2025</t>
+          <t>A 34452-2025</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -23248,10 +23248,10 @@
         </is>
       </c>
       <c r="D294" s="1" t="n">
-        <v>45882</v>
+        <v>45846</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23264,7 +23264,7 @@
         </is>
       </c>
       <c r="I294" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J294" t="n">
         <v>0</v>
@@ -23307,7 +23307,7 @@
     <row r="295" ht="15" customHeight="1">
       <c r="A295" t="inlineStr">
         <is>
-          <t>A 38122-2025</t>
+          <t>A 26882-2025</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -23321,10 +23321,10 @@
         </is>
       </c>
       <c r="D295" s="1" t="n">
-        <v>45882</v>
+        <v>45810</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23337,7 +23337,7 @@
         </is>
       </c>
       <c r="I295" t="n">
-        <v>0.8</v>
+        <v>4.2</v>
       </c>
       <c r="J295" t="n">
         <v>0</v>
@@ -23397,7 +23397,7 @@
         <v>45712</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>45712</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23543,7 +23543,7 @@
         <v>45712</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23616,7 +23616,7 @@
         <v>45737</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>

--- a/Översikt HABO.xlsx
+++ b/Översikt HABO.xlsx
@@ -601,7 +601,7 @@
         <v>45337</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>44607</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
         <v>44749</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>45534</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>45635</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>45183</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>45791</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>44877</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>45882</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>45534</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>45631</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>45811</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>45106</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>45419</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>44749</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>44824</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>45225</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>45930</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>45882</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>44801</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>45635</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>45543</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>45933</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>45813</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>45985</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>45635</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>45635</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>45882</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>45183</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>44749</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>44799</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         <v>45597</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>45747</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>45355</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>44847</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>44527</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44769</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>44846</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>44693</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         <v>44877</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>44693</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>44640</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>44670</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>44859</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>44727</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         <v>44500</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>44469</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>44623</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         <v>44799</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5452,7 +5452,7 @@
         <v>45203</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>45698</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>45698</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>45218</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>45363</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>45478</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>45450</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>45450</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         <v>45390</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
         <v>45594</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>44488</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>45469</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>45620</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6401,7 +6401,7 @@
         <v>45021</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>44939</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>45364</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         <v>45734</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6693,7 +6693,7 @@
         <v>45887</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>45882</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>46037</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>46037</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         <v>46037</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>45635</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7136,7 +7136,7 @@
         <v>46041</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>45896</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         <v>46043</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>46043</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>46043</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
         <v>46043</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>46043</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>46043</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>45597</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         <v>45646</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7871,7 +7871,7 @@
         <v>44488</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7944,7 +7944,7 @@
         <v>44488</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8017,7 +8017,7 @@
         <v>45903</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8090,7 +8090,7 @@
         <v>46052</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>45560</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8236,7 +8236,7 @@
         <v>45677</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>44628</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8382,7 +8382,7 @@
         <v>46059</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         <v>45922</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>45922</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8601,7 +8601,7 @@
         <v>45671</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>45926</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         <v>45636</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
         <v>45931</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8893,7 +8893,7 @@
         <v>45595</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>45807</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>45595</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
         <v>44749</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         <v>44995</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>45210</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>45554</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         <v>44914</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9477,7 +9477,7 @@
         <v>44816</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>45950</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         <v>45733</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         <v>45951</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9769,7 +9769,7 @@
         <v>45597</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
         <v>45812</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9920,7 +9920,7 @@
         <v>45107</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9993,7 +9993,7 @@
         <v>45810</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10066,7 +10066,7 @@
         <v>44488</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10139,7 +10139,7 @@
         <v>45972</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>45974</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
         <v>45985</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10363,7 +10363,7 @@
         <v>45985</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10441,7 +10441,7 @@
         <v>46135</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10514,7 +10514,7 @@
         <v>45982</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10587,7 +10587,7 @@
         <v>45119</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10660,7 +10660,7 @@
         <v>45119</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10733,7 +10733,7 @@
         <v>45120</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         <v>45146</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10879,7 +10879,7 @@
         <v>45660</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
         <v>45647</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11025,7 +11025,7 @@
         <v>46000</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11098,7 +11098,7 @@
         <v>45698</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11171,7 +11171,7 @@
         <v>46000</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11244,7 +11244,7 @@
         <v>46000</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11317,7 +11317,7 @@
         <v>46000</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11390,7 +11390,7 @@
         <v>45820</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>45478</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         <v>45450</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11609,7 +11609,7 @@
         <v>45450</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11682,7 +11682,7 @@
         <v>45811</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11755,7 +11755,7 @@
         <v>45698</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
         <v>45687</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11901,7 +11901,7 @@
         <v>45757</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11974,7 +11974,7 @@
         <v>45757</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12047,7 +12047,7 @@
         <v>45111</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>45621</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12193,7 +12193,7 @@
         <v>45621</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12266,7 +12266,7 @@
         <v>45113</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12339,7 +12339,7 @@
         <v>44830</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12412,7 +12412,7 @@
         <v>45007</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12485,7 +12485,7 @@
         <v>45751</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12558,7 +12558,7 @@
         <v>45173</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         <v>44876</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12704,7 +12704,7 @@
         <v>45246</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12777,7 +12777,7 @@
         <v>45827</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12850,7 +12850,7 @@
         <v>45827</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>44845</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>44894</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13069,7 +13069,7 @@
         <v>45620</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>45091</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         <v>44749</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13288,7 +13288,7 @@
         <v>45236</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>45631</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13434,7 +13434,7 @@
         <v>45558</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13507,7 +13507,7 @@
         <v>45926</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13580,7 +13580,7 @@
         <v>45099</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13653,7 +13653,7 @@
         <v>45595</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13726,7 +13726,7 @@
         <v>45636</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13799,7 +13799,7 @@
         <v>45120</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13872,7 +13872,7 @@
         <v>45846</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>45996</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14018,7 +14018,7 @@
         <v>45287</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>45810</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
         <v>45020</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>45996</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14310,7 +14310,7 @@
         <v>45397</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14383,7 +14383,7 @@
         <v>44951</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14456,7 +14456,7 @@
         <v>46171</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14529,7 +14529,7 @@
         <v>45029</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14602,7 +14602,7 @@
         <v>46176</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14675,7 +14675,7 @@
         <v>45419</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14748,7 +14748,7 @@
         <v>45149</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14821,7 +14821,7 @@
         <v>45510</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>45475</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14967,7 +14967,7 @@
         <v>45121</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15040,7 +15040,7 @@
         <v>45576</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15113,7 +15113,7 @@
         <v>45602</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15186,7 +15186,7 @@
         <v>45020</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15259,7 +15259,7 @@
         <v>45020</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15332,7 +15332,7 @@
         <v>45099</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15405,7 +15405,7 @@
         <v>45638</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15478,7 +15478,7 @@
         <v>45706</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>45621</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15624,7 +15624,7 @@
         <v>45621</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15697,7 +15697,7 @@
         <v>45621</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
         <v>45751</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15843,7 +15843,7 @@
         <v>45429</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15916,7 +15916,7 @@
         <v>45580</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>45119</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16062,7 +16062,7 @@
         <v>45119</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16135,7 +16135,7 @@
         <v>46191</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16208,7 +16208,7 @@
         <v>46191</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16281,7 +16281,7 @@
         <v>45356</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>46191</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16427,7 +16427,7 @@
         <v>46191</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16500,7 +16500,7 @@
         <v>45576</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16573,7 +16573,7 @@
         <v>45621</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16646,7 +16646,7 @@
         <v>45877</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16719,7 +16719,7 @@
         <v>45111</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16792,7 +16792,7 @@
         <v>44571</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16865,7 +16865,7 @@
         <v>45450</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16938,7 +16938,7 @@
         <v>45106</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17011,7 +17011,7 @@
         <v>45882</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17084,7 +17084,7 @@
         <v>45882</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>46203</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17235,7 +17235,7 @@
         <v>46202</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17308,7 +17308,7 @@
         <v>45882</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17381,7 +17381,7 @@
         <v>45617</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17454,7 +17454,7 @@
         <v>46203</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17527,7 +17527,7 @@
         <v>45638</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17600,7 +17600,7 @@
         <v>44783</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17678,7 +17678,7 @@
         <v>46251</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17751,7 +17751,7 @@
         <v>45597</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17829,7 +17829,7 @@
         <v>45099</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17902,7 +17902,7 @@
         <v>45687</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17975,7 +17975,7 @@
         <v>45220</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18048,7 +18048,7 @@
         <v>45316</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>45620</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18194,7 +18194,7 @@
         <v>45594</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18267,7 +18267,7 @@
         <v>45152</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>45120</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>46254</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18486,7 +18486,7 @@
         <v>45120</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18559,7 +18559,7 @@
         <v>46216</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18632,7 +18632,7 @@
         <v>45183</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18705,7 +18705,7 @@
         <v>45188</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18778,7 +18778,7 @@
         <v>45760</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18851,7 +18851,7 @@
         <v>45734</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18924,7 +18924,7 @@
         <v>45242</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19002,7 +19002,7 @@
         <v>45475</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19075,7 +19075,7 @@
         <v>45475</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19148,7 +19148,7 @@
         <v>46268</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19221,7 +19221,7 @@
         <v>46267</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19294,7 +19294,7 @@
         <v>46267</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19367,7 +19367,7 @@
         <v>46268</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19440,7 +19440,7 @@
         <v>46268</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19513,7 +19513,7 @@
         <v>46232</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
         <v>46273</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>46273</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19742,7 +19742,7 @@
         <v>45212</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19815,7 +19815,7 @@
         <v>45271</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19888,7 +19888,7 @@
         <v>45278</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19961,7 +19961,7 @@
         <v>44896</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20034,7 +20034,7 @@
         <v>44575</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20107,7 +20107,7 @@
         <v>44909</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20180,7 +20180,7 @@
         <v>45030</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20253,7 +20253,7 @@
         <v>44801</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20326,7 +20326,7 @@
         <v>46244</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20399,7 +20399,7 @@
         <v>45271</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20472,7 +20472,7 @@
         <v>46246</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20545,7 +20545,7 @@
         <v>46246</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20618,7 +20618,7 @@
         <v>44749</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20691,7 +20691,7 @@
         <v>44749</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20764,7 +20764,7 @@
         <v>44995</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20837,7 +20837,7 @@
         <v>45595</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>44797</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20983,7 +20983,7 @@
         <v>44944</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21056,7 +21056,7 @@
         <v>45152</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21129,7 +21129,7 @@
         <v>44913</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21202,7 +21202,7 @@
         <v>45030</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21275,7 +21275,7 @@
         <v>45120</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
         <v>45120</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21421,7 +21421,7 @@
         <v>45400</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21494,7 +21494,7 @@
         <v>45620</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21567,7 +21567,7 @@
         <v>44628</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>45641</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21713,7 +21713,7 @@
         <v>45091</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21786,7 +21786,7 @@
         <v>45091</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21859,7 +21859,7 @@
         <v>45204</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21932,7 +21932,7 @@
         <v>45750</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22005,7 +22005,7 @@
         <v>44775</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22078,7 +22078,7 @@
         <v>45595</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22151,7 +22151,7 @@
         <v>45307</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22224,7 +22224,7 @@
         <v>45635</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22297,7 +22297,7 @@
         <v>45222</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22370,7 +22370,7 @@
         <v>45470</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22443,7 +22443,7 @@
         <v>45372</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22516,7 +22516,7 @@
         <v>44474</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22589,7 +22589,7 @@
         <v>44877</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22662,7 +22662,7 @@
         <v>45475</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22735,7 +22735,7 @@
         <v>45217</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22808,7 +22808,7 @@
         <v>45644</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22881,7 +22881,7 @@
         <v>45469</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22959,7 +22959,7 @@
         <v>45400</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23032,7 +23032,7 @@
         <v>45777</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23105,7 +23105,7 @@
         <v>45777</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>45789</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23251,7 +23251,7 @@
         <v>45608</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23324,7 +23324,7 @@
         <v>45712</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>45712</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>45712</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23543,7 +23543,7 @@
         <v>45737</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>

--- a/Översikt HABO.xlsx
+++ b/Översikt HABO.xlsx
@@ -601,7 +601,7 @@
         <v>45337</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>44607</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
         <v>44749</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>45534</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>45635</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>45183</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>45791</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>44877</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>45882</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>45534</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>45631</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>45811</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>45106</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>45419</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>44749</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>44824</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>45225</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>45930</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>45882</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>44801</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>45635</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>45543</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>45933</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>45813</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>45985</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>45635</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>45635</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>45882</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>45183</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>44749</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>44799</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         <v>45597</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>45747</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>45355</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>44847</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>44527</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44769</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>44846</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>44693</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         <v>44877</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>44693</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>44640</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>44670</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>44859</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>44727</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         <v>44500</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>44469</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>44623</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         <v>44799</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5452,7 +5452,7 @@
         <v>45203</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>45698</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>45698</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>45218</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>45363</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>45478</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>45450</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>45450</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         <v>45390</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
         <v>45594</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>44488</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>45469</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>45620</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6401,7 +6401,7 @@
         <v>45021</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>44939</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>45364</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         <v>45734</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6693,7 +6693,7 @@
         <v>45887</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>45882</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>46037</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>46037</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         <v>46037</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>45635</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7136,7 +7136,7 @@
         <v>46041</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>45896</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         <v>46043</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>46043</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>46043</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
         <v>46043</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>46043</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>46043</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>45597</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         <v>45646</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7871,7 +7871,7 @@
         <v>44488</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7944,7 +7944,7 @@
         <v>44488</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8017,7 +8017,7 @@
         <v>45903</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8090,7 +8090,7 @@
         <v>46052</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>45560</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8236,7 +8236,7 @@
         <v>45677</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>44628</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8382,7 +8382,7 @@
         <v>46059</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         <v>45922</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>45922</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8601,7 +8601,7 @@
         <v>45671</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>45926</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         <v>45636</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
         <v>45931</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8893,7 +8893,7 @@
         <v>45595</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>45807</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>45595</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
         <v>44749</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         <v>44995</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>45210</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>45554</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         <v>44914</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9477,7 +9477,7 @@
         <v>44816</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>45950</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         <v>45733</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         <v>45951</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9769,7 +9769,7 @@
         <v>45597</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
         <v>45812</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9920,7 +9920,7 @@
         <v>45107</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9993,7 +9993,7 @@
         <v>45810</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10066,7 +10066,7 @@
         <v>44488</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10139,7 +10139,7 @@
         <v>45972</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>45974</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
         <v>45985</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10363,7 +10363,7 @@
         <v>45985</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10441,7 +10441,7 @@
         <v>46135</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10514,7 +10514,7 @@
         <v>45982</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10587,7 +10587,7 @@
         <v>45119</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10660,7 +10660,7 @@
         <v>45119</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10733,7 +10733,7 @@
         <v>45120</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         <v>45146</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10879,7 +10879,7 @@
         <v>45660</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
         <v>45647</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11025,7 +11025,7 @@
         <v>46000</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11098,7 +11098,7 @@
         <v>45698</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11171,7 +11171,7 @@
         <v>46000</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11244,7 +11244,7 @@
         <v>46000</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11317,7 +11317,7 @@
         <v>46000</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11390,7 +11390,7 @@
         <v>45820</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>45478</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         <v>45450</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11609,7 +11609,7 @@
         <v>45450</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11682,7 +11682,7 @@
         <v>45811</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11755,7 +11755,7 @@
         <v>45698</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
         <v>45687</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11901,7 +11901,7 @@
         <v>45757</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11974,7 +11974,7 @@
         <v>45757</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12047,7 +12047,7 @@
         <v>45111</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>45621</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12193,7 +12193,7 @@
         <v>45621</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12266,7 +12266,7 @@
         <v>45113</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12339,7 +12339,7 @@
         <v>44830</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12412,7 +12412,7 @@
         <v>45007</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12485,7 +12485,7 @@
         <v>45751</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12558,7 +12558,7 @@
         <v>45173</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         <v>44876</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12704,7 +12704,7 @@
         <v>45246</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12777,7 +12777,7 @@
         <v>45827</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12850,7 +12850,7 @@
         <v>45827</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>44845</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>44894</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13069,7 +13069,7 @@
         <v>45620</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>45091</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         <v>44749</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13288,7 +13288,7 @@
         <v>45236</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>45631</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13434,7 +13434,7 @@
         <v>45558</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13507,7 +13507,7 @@
         <v>45926</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13580,7 +13580,7 @@
         <v>45099</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13653,7 +13653,7 @@
         <v>45595</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13726,7 +13726,7 @@
         <v>45636</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13799,7 +13799,7 @@
         <v>45120</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13872,7 +13872,7 @@
         <v>45846</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>45996</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14018,7 +14018,7 @@
         <v>45287</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>45810</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
         <v>45020</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>45996</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14310,7 +14310,7 @@
         <v>45397</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14383,7 +14383,7 @@
         <v>44951</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14456,7 +14456,7 @@
         <v>46171</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14529,7 +14529,7 @@
         <v>45029</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14602,7 +14602,7 @@
         <v>46176</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14675,7 +14675,7 @@
         <v>45419</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14748,7 +14748,7 @@
         <v>45149</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14821,7 +14821,7 @@
         <v>45510</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>45475</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14967,7 +14967,7 @@
         <v>45121</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15040,7 +15040,7 @@
         <v>45576</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15113,7 +15113,7 @@
         <v>45602</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15186,7 +15186,7 @@
         <v>45020</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15259,7 +15259,7 @@
         <v>45020</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15332,7 +15332,7 @@
         <v>45099</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15405,7 +15405,7 @@
         <v>45638</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15478,7 +15478,7 @@
         <v>45706</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>45621</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15624,7 +15624,7 @@
         <v>45621</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15697,7 +15697,7 @@
         <v>45621</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
         <v>45751</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15843,7 +15843,7 @@
         <v>45429</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15916,7 +15916,7 @@
         <v>45580</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>45119</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16062,7 +16062,7 @@
         <v>45119</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16135,7 +16135,7 @@
         <v>46191</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16208,7 +16208,7 @@
         <v>46191</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16281,7 +16281,7 @@
         <v>45356</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>46191</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16427,7 +16427,7 @@
         <v>46191</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16500,7 +16500,7 @@
         <v>45576</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16573,7 +16573,7 @@
         <v>45621</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16646,7 +16646,7 @@
         <v>45877</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16719,7 +16719,7 @@
         <v>45111</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16792,7 +16792,7 @@
         <v>44571</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16865,7 +16865,7 @@
         <v>45450</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16938,7 +16938,7 @@
         <v>45106</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17011,7 +17011,7 @@
         <v>45882</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17084,7 +17084,7 @@
         <v>45882</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>46203</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17235,7 +17235,7 @@
         <v>46202</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17308,7 +17308,7 @@
         <v>45882</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17381,7 +17381,7 @@
         <v>45617</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17454,7 +17454,7 @@
         <v>46203</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17527,7 +17527,7 @@
         <v>45638</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17600,7 +17600,7 @@
         <v>44783</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17678,7 +17678,7 @@
         <v>46251</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17751,7 +17751,7 @@
         <v>45597</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17829,7 +17829,7 @@
         <v>45099</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17902,7 +17902,7 @@
         <v>45687</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17975,7 +17975,7 @@
         <v>45220</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18048,7 +18048,7 @@
         <v>45316</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>45620</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18194,7 +18194,7 @@
         <v>45594</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18267,7 +18267,7 @@
         <v>45152</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>45120</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>46254</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18486,7 +18486,7 @@
         <v>45120</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18559,7 +18559,7 @@
         <v>46216</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18632,7 +18632,7 @@
         <v>45183</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18705,7 +18705,7 @@
         <v>45188</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18778,7 +18778,7 @@
         <v>45760</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18851,7 +18851,7 @@
         <v>45734</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18924,7 +18924,7 @@
         <v>45242</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19002,7 +19002,7 @@
         <v>45475</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19075,7 +19075,7 @@
         <v>45475</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19148,7 +19148,7 @@
         <v>46268</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19221,7 +19221,7 @@
         <v>46267</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19294,7 +19294,7 @@
         <v>46267</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19367,7 +19367,7 @@
         <v>46268</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19440,7 +19440,7 @@
         <v>46268</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19513,7 +19513,7 @@
         <v>46232</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
         <v>46273</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>46273</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19742,7 +19742,7 @@
         <v>45212</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19815,7 +19815,7 @@
         <v>45271</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19888,7 +19888,7 @@
         <v>45278</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19961,7 +19961,7 @@
         <v>44896</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20034,7 +20034,7 @@
         <v>44575</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20107,7 +20107,7 @@
         <v>44909</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20180,7 +20180,7 @@
         <v>45030</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20253,7 +20253,7 @@
         <v>44801</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20326,7 +20326,7 @@
         <v>46244</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20399,7 +20399,7 @@
         <v>45271</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20472,7 +20472,7 @@
         <v>46246</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20545,7 +20545,7 @@
         <v>46246</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20618,7 +20618,7 @@
         <v>44749</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20691,7 +20691,7 @@
         <v>44749</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20764,7 +20764,7 @@
         <v>44995</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20837,7 +20837,7 @@
         <v>45595</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>44797</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20983,7 +20983,7 @@
         <v>44944</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21056,7 +21056,7 @@
         <v>45152</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21129,7 +21129,7 @@
         <v>44913</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21202,7 +21202,7 @@
         <v>45030</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21275,7 +21275,7 @@
         <v>45120</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
         <v>45120</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21421,7 +21421,7 @@
         <v>45400</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21494,7 +21494,7 @@
         <v>45620</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21567,7 +21567,7 @@
         <v>44628</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>45641</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21713,7 +21713,7 @@
         <v>45091</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21786,7 +21786,7 @@
         <v>45091</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21859,7 +21859,7 @@
         <v>45204</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21932,7 +21932,7 @@
         <v>45750</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22005,7 +22005,7 @@
         <v>44775</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22078,7 +22078,7 @@
         <v>45595</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22151,7 +22151,7 @@
         <v>45307</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22224,7 +22224,7 @@
         <v>45635</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22297,7 +22297,7 @@
         <v>45222</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22370,7 +22370,7 @@
         <v>45470</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22443,7 +22443,7 @@
         <v>45372</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22516,7 +22516,7 @@
         <v>44474</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22589,7 +22589,7 @@
         <v>44877</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22662,7 +22662,7 @@
         <v>45475</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22735,7 +22735,7 @@
         <v>45217</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22808,7 +22808,7 @@
         <v>45644</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22881,7 +22881,7 @@
         <v>45469</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22959,7 +22959,7 @@
         <v>45400</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23032,7 +23032,7 @@
         <v>45777</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23105,7 +23105,7 @@
         <v>45777</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>45789</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23251,7 +23251,7 @@
         <v>45608</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23324,7 +23324,7 @@
         <v>45712</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>45712</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>45712</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23543,7 +23543,7 @@
         <v>45737</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>

--- a/Översikt HABO.xlsx
+++ b/Översikt HABO.xlsx
@@ -601,7 +601,7 @@
         <v>45337</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>44607</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
         <v>44749</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>45534</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>45791</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45183</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>45635</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>44877</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>45882</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>45811</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>44749</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>45419</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>45534</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>45106</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>45631</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>44824</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>45930</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>45882</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>45225</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>44801</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>45635</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>45543</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>44749</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>45933</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>45597</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>45813</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>45985</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>45635</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>45747</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>44799</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>45882</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4027,7 +4027,7 @@
         <v>45635</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>45183</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>45355</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>44847</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>44527</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44769</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>44846</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>44693</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         <v>44877</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>44693</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>44640</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>44670</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>44859</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>44727</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         <v>44500</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>44623</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>45475</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         <v>45212</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5452,7 +5452,7 @@
         <v>45091</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>45029</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>45660</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>45641</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>45698</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>45636</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>44801</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>45111</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         <v>45687</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
         <v>45597</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>45030</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>44488</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         <v>45478</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>45620</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         <v>45621</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6552,7 +6552,7 @@
         <v>45621</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6625,7 +6625,7 @@
         <v>45621</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         <v>45887</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>45608</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>44571</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>45896</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         <v>45475</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>45475</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7136,7 +7136,7 @@
         <v>45120</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>45903</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         <v>46037</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>46037</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>45146</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
         <v>46037</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>46041</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>46043</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>46043</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         <v>46043</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>46043</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         <v>45602</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>46043</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>46043</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>45364</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>45021</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>45734</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         <v>45621</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         <v>44783</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>45922</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8601,7 +8601,7 @@
         <v>45807</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>45922</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         <v>46052</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
         <v>45595</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8893,7 +8893,7 @@
         <v>45595</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>45926</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>45030</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
         <v>46059</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         <v>44951</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>45931</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>45210</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         <v>45278</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9477,7 +9477,7 @@
         <v>45475</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>45621</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         <v>45621</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         <v>45810</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9769,7 +9769,7 @@
         <v>44896</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9842,7 +9842,7 @@
         <v>45597</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9920,7 +9920,7 @@
         <v>45950</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9993,7 +9993,7 @@
         <v>45951</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10066,7 +10066,7 @@
         <v>45560</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10139,7 +10139,7 @@
         <v>45107</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>44799</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
         <v>45812</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
         <v>45121</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10431,7 +10431,7 @@
         <v>45149</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
         <v>44749</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10577,7 +10577,7 @@
         <v>44749</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10650,7 +10650,7 @@
         <v>45635</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10723,7 +10723,7 @@
         <v>45111</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10796,7 +10796,7 @@
         <v>45972</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10869,7 +10869,7 @@
         <v>45974</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
         <v>45091</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11015,7 +11015,7 @@
         <v>45671</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11088,7 +11088,7 @@
         <v>45099</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11161,7 +11161,7 @@
         <v>45099</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11234,7 +11234,7 @@
         <v>45469</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11307,7 +11307,7 @@
         <v>45646</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11380,7 +11380,7 @@
         <v>45811</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11453,7 +11453,7 @@
         <v>45985</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         <v>45985</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11609,7 +11609,7 @@
         <v>45982</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11682,7 +11682,7 @@
         <v>45827</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11755,7 +11755,7 @@
         <v>44816</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
         <v>44845</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11901,7 +11901,7 @@
         <v>45827</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11974,7 +11974,7 @@
         <v>46000</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12047,7 +12047,7 @@
         <v>46000</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>46000</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12193,7 +12193,7 @@
         <v>46000</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12266,7 +12266,7 @@
         <v>45760</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12339,7 +12339,7 @@
         <v>44474</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12412,7 +12412,7 @@
         <v>46135</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12485,7 +12485,7 @@
         <v>45698</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12558,7 +12558,7 @@
         <v>44944</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         <v>45846</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12704,7 +12704,7 @@
         <v>45620</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12777,7 +12777,7 @@
         <v>44628</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12850,7 +12850,7 @@
         <v>45810</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>44575</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>45020</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13069,7 +13069,7 @@
         <v>45020</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>45820</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         <v>45222</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13288,7 +13288,7 @@
         <v>45173</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>45558</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13434,7 +13434,7 @@
         <v>44894</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13507,7 +13507,7 @@
         <v>45469</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13585,7 +13585,7 @@
         <v>44749</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13658,7 +13658,7 @@
         <v>44749</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13731,7 +13731,7 @@
         <v>45246</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13804,7 +13804,7 @@
         <v>45751</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13877,7 +13877,7 @@
         <v>45751</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13950,7 +13950,7 @@
         <v>44628</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14023,7 +14023,7 @@
         <v>45099</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14096,7 +14096,7 @@
         <v>45429</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14169,7 +14169,7 @@
         <v>45400</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14242,7 +14242,7 @@
         <v>45188</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14315,7 +14315,7 @@
         <v>45450</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14388,7 +14388,7 @@
         <v>45597</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14466,7 +14466,7 @@
         <v>45706</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14539,7 +14539,7 @@
         <v>45120</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14612,7 +14612,7 @@
         <v>45478</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14685,7 +14685,7 @@
         <v>45926</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>45020</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14831,7 +14831,7 @@
         <v>45877</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14904,7 +14904,7 @@
         <v>45698</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14977,7 +14977,7 @@
         <v>45698</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15050,7 +15050,7 @@
         <v>45595</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15123,7 +15123,7 @@
         <v>45996</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>45996</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15269,7 +15269,7 @@
         <v>44797</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15342,7 +15342,7 @@
         <v>46171</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15415,7 +15415,7 @@
         <v>44913</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15488,7 +15488,7 @@
         <v>45882</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15566,7 +15566,7 @@
         <v>45882</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15639,7 +15639,7 @@
         <v>45287</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>45882</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15785,7 +15785,7 @@
         <v>45419</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         <v>46176</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>45617</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>45882</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16082,7 +16082,7 @@
         <v>45750</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16155,7 +16155,7 @@
         <v>45271</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16228,7 +16228,7 @@
         <v>45638</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>45450</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16374,7 +16374,7 @@
         <v>45450</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16447,7 +16447,7 @@
         <v>46191</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16520,7 +16520,7 @@
         <v>46191</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16593,7 +16593,7 @@
         <v>46191</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16666,7 +16666,7 @@
         <v>46191</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16739,7 +16739,7 @@
         <v>45576</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16812,7 +16812,7 @@
         <v>45183</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16885,7 +16885,7 @@
         <v>45271</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16958,7 +16958,7 @@
         <v>44876</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17031,7 +17031,7 @@
         <v>46203</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17104,7 +17104,7 @@
         <v>45242</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17182,7 +17182,7 @@
         <v>46203</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17255,7 +17255,7 @@
         <v>44830</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17328,7 +17328,7 @@
         <v>46202</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17401,7 +17401,7 @@
         <v>45677</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17474,7 +17474,7 @@
         <v>45218</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         <v>45203</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17620,7 +17620,7 @@
         <v>45638</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17693,7 +17693,7 @@
         <v>45316</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17766,7 +17766,7 @@
         <v>45594</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17839,7 +17839,7 @@
         <v>45733</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17912,7 +17912,7 @@
         <v>46216</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17985,7 +17985,7 @@
         <v>45594</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>45595</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18131,7 +18131,7 @@
         <v>45470</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18204,7 +18204,7 @@
         <v>45620</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18277,7 +18277,7 @@
         <v>45620</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18350,7 +18350,7 @@
         <v>46267</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18423,7 +18423,7 @@
         <v>45450</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18496,7 +18496,7 @@
         <v>45450</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18569,7 +18569,7 @@
         <v>45400</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18642,7 +18642,7 @@
         <v>46267</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>46268</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>46268</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18861,7 +18861,7 @@
         <v>46268</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>46273</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19012,7 +19012,7 @@
         <v>45734</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19085,7 +19085,7 @@
         <v>46273</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19163,7 +19163,7 @@
         <v>46232</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19236,7 +19236,7 @@
         <v>45113</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19309,7 +19309,7 @@
         <v>45554</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19382,7 +19382,7 @@
         <v>45236</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19455,7 +19455,7 @@
         <v>45220</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19528,7 +19528,7 @@
         <v>45356</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19601,7 +19601,7 @@
         <v>46244</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19674,7 +19674,7 @@
         <v>44939</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19747,7 +19747,7 @@
         <v>44995</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19820,7 +19820,7 @@
         <v>45091</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>46246</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>44877</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20039,7 +20039,7 @@
         <v>45397</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20112,7 +20112,7 @@
         <v>45307</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20185,7 +20185,7 @@
         <v>45580</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20258,7 +20258,7 @@
         <v>45007</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20331,7 +20331,7 @@
         <v>45152</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20404,7 +20404,7 @@
         <v>45510</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20477,7 +20477,7 @@
         <v>45576</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20550,7 +20550,7 @@
         <v>45635</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20623,7 +20623,7 @@
         <v>45757</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20696,7 +20696,7 @@
         <v>45757</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20769,7 +20769,7 @@
         <v>46251</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20842,7 +20842,7 @@
         <v>45204</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20915,7 +20915,7 @@
         <v>45595</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20988,7 +20988,7 @@
         <v>45390</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21061,7 +21061,7 @@
         <v>46254</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21134,7 +21134,7 @@
         <v>46246</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21207,7 +21207,7 @@
         <v>45631</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21280,7 +21280,7 @@
         <v>44909</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21353,7 +21353,7 @@
         <v>45372</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>45647</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21499,7 +21499,7 @@
         <v>44488</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21572,7 +21572,7 @@
         <v>45636</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21645,7 +21645,7 @@
         <v>45644</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21718,7 +21718,7 @@
         <v>45120</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21791,7 +21791,7 @@
         <v>45119</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21864,7 +21864,7 @@
         <v>45119</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>44488</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>44488</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22083,7 +22083,7 @@
         <v>45119</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22156,7 +22156,7 @@
         <v>45152</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22229,7 +22229,7 @@
         <v>44995</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22302,7 +22302,7 @@
         <v>45363</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22375,7 +22375,7 @@
         <v>44914</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22448,7 +22448,7 @@
         <v>45217</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
         <v>45106</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22594,7 +22594,7 @@
         <v>45119</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22667,7 +22667,7 @@
         <v>45120</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22740,7 +22740,7 @@
         <v>45120</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22813,7 +22813,7 @@
         <v>45120</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22886,7 +22886,7 @@
         <v>45687</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22959,7 +22959,7 @@
         <v>44775</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23032,7 +23032,7 @@
         <v>45777</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23105,7 +23105,7 @@
         <v>45777</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>45789</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23251,7 +23251,7 @@
         <v>45712</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23324,7 +23324,7 @@
         <v>45712</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>45712</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>45737</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>

--- a/Översikt HABO.xlsx
+++ b/Översikt HABO.xlsx
@@ -601,7 +601,7 @@
         <v>45337</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>44607</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
         <v>44749</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>45534</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>45791</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45183</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>45635</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>44877</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>45882</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>45811</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>44749</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>45419</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>45534</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>45106</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>45631</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>44824</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>45930</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>45882</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>45225</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>44801</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>45635</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>45543</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>44749</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>45933</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>45597</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>45813</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>45985</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>45635</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>45747</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>44799</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>45882</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4027,7 +4027,7 @@
         <v>45635</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>45183</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>45355</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>44847</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>44527</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44769</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>44846</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>44693</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         <v>44877</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>44693</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>44640</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>44670</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>44859</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>44727</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         <v>44500</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>44623</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>45475</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         <v>45212</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5452,7 +5452,7 @@
         <v>45091</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>45029</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>45660</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>45641</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>45698</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>45636</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>44801</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>45111</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         <v>45687</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
         <v>45597</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>45030</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>44488</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         <v>45478</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>45620</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         <v>45621</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6552,7 +6552,7 @@
         <v>45621</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6625,7 +6625,7 @@
         <v>45621</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         <v>45887</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>45608</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>44571</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>45896</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         <v>45475</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>45475</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7136,7 +7136,7 @@
         <v>45120</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>45903</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         <v>46037</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>46037</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>45146</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
         <v>46037</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>46041</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>46043</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>46043</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         <v>46043</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>46043</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         <v>45602</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>46043</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>46043</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>45364</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>45021</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>45734</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         <v>45621</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         <v>44783</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>45922</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8601,7 +8601,7 @@
         <v>45807</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>45922</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         <v>46052</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
         <v>45595</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8893,7 +8893,7 @@
         <v>45595</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>45926</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>45030</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
         <v>46059</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         <v>44951</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>45931</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>45210</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         <v>45278</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9477,7 +9477,7 @@
         <v>45475</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>45621</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         <v>45621</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         <v>45810</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9769,7 +9769,7 @@
         <v>44896</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9842,7 +9842,7 @@
         <v>45597</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9920,7 +9920,7 @@
         <v>45950</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9993,7 +9993,7 @@
         <v>45951</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10066,7 +10066,7 @@
         <v>45560</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10139,7 +10139,7 @@
         <v>45107</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>44799</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
         <v>45812</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
         <v>45121</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10431,7 +10431,7 @@
         <v>45149</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
         <v>44749</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10577,7 +10577,7 @@
         <v>44749</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10650,7 +10650,7 @@
         <v>45635</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10723,7 +10723,7 @@
         <v>45111</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10796,7 +10796,7 @@
         <v>45972</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10869,7 +10869,7 @@
         <v>45974</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
         <v>45091</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11015,7 +11015,7 @@
         <v>45671</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11088,7 +11088,7 @@
         <v>45099</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11161,7 +11161,7 @@
         <v>45099</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11234,7 +11234,7 @@
         <v>45469</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11307,7 +11307,7 @@
         <v>45646</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11380,7 +11380,7 @@
         <v>45811</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11453,7 +11453,7 @@
         <v>45985</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         <v>45985</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11609,7 +11609,7 @@
         <v>45982</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11682,7 +11682,7 @@
         <v>45827</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11755,7 +11755,7 @@
         <v>44816</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
         <v>44845</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11901,7 +11901,7 @@
         <v>45827</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11974,7 +11974,7 @@
         <v>46000</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12047,7 +12047,7 @@
         <v>46000</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>46000</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12193,7 +12193,7 @@
         <v>46000</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12266,7 +12266,7 @@
         <v>45760</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12339,7 +12339,7 @@
         <v>44474</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12412,7 +12412,7 @@
         <v>46135</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12485,7 +12485,7 @@
         <v>45698</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12558,7 +12558,7 @@
         <v>44944</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         <v>45846</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12704,7 +12704,7 @@
         <v>45620</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12777,7 +12777,7 @@
         <v>44628</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12850,7 +12850,7 @@
         <v>45810</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>44575</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>45020</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13069,7 +13069,7 @@
         <v>45020</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>45820</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         <v>45222</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13288,7 +13288,7 @@
         <v>45173</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>45558</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13434,7 +13434,7 @@
         <v>44894</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13507,7 +13507,7 @@
         <v>45469</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13585,7 +13585,7 @@
         <v>44749</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13658,7 +13658,7 @@
         <v>44749</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13731,7 +13731,7 @@
         <v>45246</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13804,7 +13804,7 @@
         <v>45751</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13877,7 +13877,7 @@
         <v>45751</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13950,7 +13950,7 @@
         <v>44628</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14023,7 +14023,7 @@
         <v>45099</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14096,7 +14096,7 @@
         <v>45429</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14169,7 +14169,7 @@
         <v>45400</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14242,7 +14242,7 @@
         <v>45188</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14315,7 +14315,7 @@
         <v>45450</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14388,7 +14388,7 @@
         <v>45597</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14466,7 +14466,7 @@
         <v>45706</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14539,7 +14539,7 @@
         <v>45120</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14612,7 +14612,7 @@
         <v>45478</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14685,7 +14685,7 @@
         <v>45926</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>45020</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14831,7 +14831,7 @@
         <v>45877</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14904,7 +14904,7 @@
         <v>45698</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14977,7 +14977,7 @@
         <v>45698</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15050,7 +15050,7 @@
         <v>45595</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15123,7 +15123,7 @@
         <v>45996</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>45996</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15269,7 +15269,7 @@
         <v>44797</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15342,7 +15342,7 @@
         <v>46171</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15415,7 +15415,7 @@
         <v>44913</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15488,7 +15488,7 @@
         <v>45882</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15566,7 +15566,7 @@
         <v>45882</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15639,7 +15639,7 @@
         <v>45287</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>45882</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15785,7 +15785,7 @@
         <v>45419</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         <v>46176</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>45617</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>45882</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16082,7 +16082,7 @@
         <v>45750</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16155,7 +16155,7 @@
         <v>45271</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16228,7 +16228,7 @@
         <v>45638</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>45450</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16374,7 +16374,7 @@
         <v>45450</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16447,7 +16447,7 @@
         <v>46191</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16520,7 +16520,7 @@
         <v>46191</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16593,7 +16593,7 @@
         <v>46191</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16666,7 +16666,7 @@
         <v>46191</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16739,7 +16739,7 @@
         <v>45576</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16812,7 +16812,7 @@
         <v>45183</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16885,7 +16885,7 @@
         <v>45271</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16958,7 +16958,7 @@
         <v>44876</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17031,7 +17031,7 @@
         <v>46203</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17104,7 +17104,7 @@
         <v>45242</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17182,7 +17182,7 @@
         <v>46203</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17255,7 +17255,7 @@
         <v>44830</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17328,7 +17328,7 @@
         <v>46202</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17401,7 +17401,7 @@
         <v>45677</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17474,7 +17474,7 @@
         <v>45218</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         <v>45203</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17620,7 +17620,7 @@
         <v>45638</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17693,7 +17693,7 @@
         <v>45316</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17766,7 +17766,7 @@
         <v>45594</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17839,7 +17839,7 @@
         <v>45733</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17912,7 +17912,7 @@
         <v>46216</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17985,7 +17985,7 @@
         <v>45594</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>45595</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18131,7 +18131,7 @@
         <v>45470</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18204,7 +18204,7 @@
         <v>45620</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18277,7 +18277,7 @@
         <v>45620</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18350,7 +18350,7 @@
         <v>46267</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18423,7 +18423,7 @@
         <v>45450</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18496,7 +18496,7 @@
         <v>45450</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18569,7 +18569,7 @@
         <v>45400</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18642,7 +18642,7 @@
         <v>46267</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>46268</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>46268</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18861,7 +18861,7 @@
         <v>46268</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>46273</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19012,7 +19012,7 @@
         <v>45734</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19085,7 +19085,7 @@
         <v>46273</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19163,7 +19163,7 @@
         <v>46232</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19236,7 +19236,7 @@
         <v>45113</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19309,7 +19309,7 @@
         <v>45554</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19382,7 +19382,7 @@
         <v>45236</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19455,7 +19455,7 @@
         <v>45220</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19528,7 +19528,7 @@
         <v>45356</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19601,7 +19601,7 @@
         <v>46244</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19674,7 +19674,7 @@
         <v>44939</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19747,7 +19747,7 @@
         <v>44995</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19820,7 +19820,7 @@
         <v>45091</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>46246</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>44877</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20039,7 +20039,7 @@
         <v>45397</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20112,7 +20112,7 @@
         <v>45307</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20185,7 +20185,7 @@
         <v>45580</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20258,7 +20258,7 @@
         <v>45007</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20331,7 +20331,7 @@
         <v>45152</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20404,7 +20404,7 @@
         <v>45510</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20477,7 +20477,7 @@
         <v>45576</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20550,7 +20550,7 @@
         <v>45635</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20623,7 +20623,7 @@
         <v>45757</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20696,7 +20696,7 @@
         <v>45757</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20769,7 +20769,7 @@
         <v>46251</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20842,7 +20842,7 @@
         <v>45204</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20915,7 +20915,7 @@
         <v>45595</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20988,7 +20988,7 @@
         <v>45390</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21061,7 +21061,7 @@
         <v>46254</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21134,7 +21134,7 @@
         <v>46246</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21207,7 +21207,7 @@
         <v>45631</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21280,7 +21280,7 @@
         <v>44909</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21353,7 +21353,7 @@
         <v>45372</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>45647</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21499,7 +21499,7 @@
         <v>44488</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21572,7 +21572,7 @@
         <v>45636</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21645,7 +21645,7 @@
         <v>45644</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21718,7 +21718,7 @@
         <v>45120</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21791,7 +21791,7 @@
         <v>45119</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21864,7 +21864,7 @@
         <v>45119</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>44488</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>44488</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22083,7 +22083,7 @@
         <v>45119</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22156,7 +22156,7 @@
         <v>45152</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22229,7 +22229,7 @@
         <v>44995</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22302,7 +22302,7 @@
         <v>45363</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22375,7 +22375,7 @@
         <v>44914</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22448,7 +22448,7 @@
         <v>45217</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
         <v>45106</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22594,7 +22594,7 @@
         <v>45119</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22667,7 +22667,7 @@
         <v>45120</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22740,7 +22740,7 @@
         <v>45120</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22813,7 +22813,7 @@
         <v>45120</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22886,7 +22886,7 @@
         <v>45687</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22959,7 +22959,7 @@
         <v>44775</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23032,7 +23032,7 @@
         <v>45777</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23105,7 +23105,7 @@
         <v>45777</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>45789</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23251,7 +23251,7 @@
         <v>45712</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23324,7 +23324,7 @@
         <v>45712</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>45712</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>45737</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>

--- a/Översikt HABO.xlsx
+++ b/Översikt HABO.xlsx
@@ -601,7 +601,7 @@
         <v>45337</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>44607</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
         <v>44749</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>45534</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>45635</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>45791</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>45183</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>44877</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>45882</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>44749</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>45534</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>45811</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>45631</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>45106</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>45419</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>44824</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>45225</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>45635</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>45930</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>44801</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>45882</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>45597</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>45747</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         <v>45635</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
         <v>45543</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         <v>45183</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         <v>45933</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>45813</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>44749</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>45635</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>45882</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>45985</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>44799</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>45355</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>44847</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>44527</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44769</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>44846</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>44693</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         <v>44877</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>44670</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>44500</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>44859</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>44693</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>44640</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         <v>45203</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>44623</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>44727</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         <v>44628</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5452,7 +5452,7 @@
         <v>45091</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>45698</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>45698</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>44749</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>44799</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>45218</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>45363</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>45236</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         <v>45641</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
         <v>45631</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>45558</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>45091</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>45091</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6401,7 +6401,7 @@
         <v>45099</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>45204</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>45636</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         <v>45120</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6693,7 +6693,7 @@
         <v>45750</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>44775</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>45595</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>45307</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
         <v>45478</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         <v>45390</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>45450</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>45450</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>45635</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7350,7 +7350,7 @@
         <v>45222</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7423,7 +7423,7 @@
         <v>45287</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7496,7 +7496,7 @@
         <v>45020</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7569,7 +7569,7 @@
         <v>45397</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7642,7 +7642,7 @@
         <v>45470</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>45372</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>44488</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7861,7 +7861,7 @@
         <v>45594</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         <v>45887</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>45882</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>44877</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>44951</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>45469</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>45620</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         <v>44939</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         <v>45475</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         <v>45896</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8596,7 +8596,7 @@
         <v>45217</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         <v>45029</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8742,7 +8742,7 @@
         <v>45903</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         <v>45635</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
         <v>45644</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         <v>45419</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9034,7 +9034,7 @@
         <v>45149</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9107,7 +9107,7 @@
         <v>45510</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         <v>45469</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>45475</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>45121</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         <v>45576</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9477,7 +9477,7 @@
         <v>45400</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>45597</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9628,7 +9628,7 @@
         <v>45646</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9701,7 +9701,7 @@
         <v>45602</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9774,7 +9774,7 @@
         <v>44488</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
         <v>44488</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9920,7 +9920,7 @@
         <v>45777</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9993,7 +9993,7 @@
         <v>45777</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10066,7 +10066,7 @@
         <v>45020</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10139,7 +10139,7 @@
         <v>45020</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>45099</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
         <v>45560</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
         <v>45638</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10431,7 +10431,7 @@
         <v>45677</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
         <v>44628</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10577,7 +10577,7 @@
         <v>45706</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10650,7 +10650,7 @@
         <v>45621</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10723,7 +10723,7 @@
         <v>45621</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10796,7 +10796,7 @@
         <v>45621</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10869,7 +10869,7 @@
         <v>45429</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
         <v>45922</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11015,7 +11015,7 @@
         <v>45789</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11088,7 +11088,7 @@
         <v>45922</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11161,7 +11161,7 @@
         <v>45580</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11234,7 +11234,7 @@
         <v>45119</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11307,7 +11307,7 @@
         <v>45119</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11380,7 +11380,7 @@
         <v>45356</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11453,7 +11453,7 @@
         <v>45671</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11526,7 +11526,7 @@
         <v>45576</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11599,7 +11599,7 @@
         <v>45926</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11672,7 +11672,7 @@
         <v>45621</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11745,7 +11745,7 @@
         <v>45636</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
         <v>45608</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11891,7 +11891,7 @@
         <v>45111</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11964,7 +11964,7 @@
         <v>44571</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12037,7 +12037,7 @@
         <v>45931</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12110,7 +12110,7 @@
         <v>45595</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12183,7 +12183,7 @@
         <v>45595</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12256,7 +12256,7 @@
         <v>44749</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
         <v>45450</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12402,7 +12402,7 @@
         <v>45106</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12475,7 +12475,7 @@
         <v>45021</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12548,7 +12548,7 @@
         <v>44995</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12621,7 +12621,7 @@
         <v>45364</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12694,7 +12694,7 @@
         <v>45734</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         <v>45210</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12840,7 +12840,7 @@
         <v>45554</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12913,7 +12913,7 @@
         <v>45617</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12986,7 +12986,7 @@
         <v>45638</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13059,7 +13059,7 @@
         <v>44783</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13137,7 +13137,7 @@
         <v>45597</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         <v>45099</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13288,7 +13288,7 @@
         <v>44914</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>44816</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13434,7 +13434,7 @@
         <v>45807</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13507,7 +13507,7 @@
         <v>45733</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13580,7 +13580,7 @@
         <v>45687</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13653,7 +13653,7 @@
         <v>45812</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13726,7 +13726,7 @@
         <v>45220</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13799,7 +13799,7 @@
         <v>45597</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13877,7 +13877,7 @@
         <v>45620</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13950,7 +13950,7 @@
         <v>45810</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14023,7 +14023,7 @@
         <v>45152</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14096,7 +14096,7 @@
         <v>45120</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14169,7 +14169,7 @@
         <v>45950</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14242,7 +14242,7 @@
         <v>45107</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14315,7 +14315,7 @@
         <v>45811</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14388,7 +14388,7 @@
         <v>45120</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14461,7 +14461,7 @@
         <v>45951</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14534,7 +14534,7 @@
         <v>44488</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14607,7 +14607,7 @@
         <v>45827</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14680,7 +14680,7 @@
         <v>45827</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14753,7 +14753,7 @@
         <v>45183</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14826,7 +14826,7 @@
         <v>45188</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14899,7 +14899,7 @@
         <v>45972</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14972,7 +14972,7 @@
         <v>45760</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15045,7 +15045,7 @@
         <v>45119</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15118,7 +15118,7 @@
         <v>45119</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15191,7 +15191,7 @@
         <v>45120</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15264,7 +15264,7 @@
         <v>45974</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15337,7 +15337,7 @@
         <v>45846</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15410,7 +15410,7 @@
         <v>45734</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15483,7 +15483,7 @@
         <v>45242</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15561,7 +15561,7 @@
         <v>45475</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15634,7 +15634,7 @@
         <v>45475</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15707,7 +15707,7 @@
         <v>45146</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15780,7 +15780,7 @@
         <v>45810</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15853,7 +15853,7 @@
         <v>45660</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15926,7 +15926,7 @@
         <v>45647</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>45478</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16072,7 +16072,7 @@
         <v>45450</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16145,7 +16145,7 @@
         <v>45450</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16218,7 +16218,7 @@
         <v>45751</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16291,7 +16291,7 @@
         <v>45698</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>45687</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16437,7 +16437,7 @@
         <v>45212</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16510,7 +16510,7 @@
         <v>45877</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16583,7 +16583,7 @@
         <v>45757</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16656,7 +16656,7 @@
         <v>45757</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16729,7 +16729,7 @@
         <v>45271</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16802,7 +16802,7 @@
         <v>45111</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16875,7 +16875,7 @@
         <v>45882</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16948,7 +16948,7 @@
         <v>45621</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17021,7 +17021,7 @@
         <v>45621</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17094,7 +17094,7 @@
         <v>45882</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17172,7 +17172,7 @@
         <v>45882</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17245,7 +17245,7 @@
         <v>45113</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>44830</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17391,7 +17391,7 @@
         <v>45278</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17464,7 +17464,7 @@
         <v>45007</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17537,7 +17537,7 @@
         <v>45985</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         <v>45985</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17693,7 +17693,7 @@
         <v>45751</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17766,7 +17766,7 @@
         <v>44896</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17839,7 +17839,7 @@
         <v>45173</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17912,7 +17912,7 @@
         <v>44876</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17985,7 +17985,7 @@
         <v>45982</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>44845</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18131,7 +18131,7 @@
         <v>44894</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18204,7 +18204,7 @@
         <v>45620</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18277,7 +18277,7 @@
         <v>44575</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18350,7 +18350,7 @@
         <v>44909</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18423,7 +18423,7 @@
         <v>46000</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18496,7 +18496,7 @@
         <v>45030</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18569,7 +18569,7 @@
         <v>44801</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18642,7 +18642,7 @@
         <v>46000</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>46000</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>45271</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18861,7 +18861,7 @@
         <v>46000</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>46135</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19007,7 +19007,7 @@
         <v>44749</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19080,7 +19080,7 @@
         <v>44749</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19153,7 +19153,7 @@
         <v>44995</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>45595</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19299,7 +19299,7 @@
         <v>44797</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19372,7 +19372,7 @@
         <v>44944</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19445,7 +19445,7 @@
         <v>45152</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19518,7 +19518,7 @@
         <v>45698</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19591,7 +19591,7 @@
         <v>44913</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>45820</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19737,7 +19737,7 @@
         <v>46037</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19810,7 +19810,7 @@
         <v>46037</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19883,7 +19883,7 @@
         <v>46037</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
         <v>46041</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>46043</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20102,7 +20102,7 @@
         <v>46043</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20175,7 +20175,7 @@
         <v>46043</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20248,7 +20248,7 @@
         <v>46043</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20321,7 +20321,7 @@
         <v>46043</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20394,7 +20394,7 @@
         <v>46043</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20467,7 +20467,7 @@
         <v>45030</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20540,7 +20540,7 @@
         <v>45120</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20613,7 +20613,7 @@
         <v>45120</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20686,7 +20686,7 @@
         <v>45400</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20759,7 +20759,7 @@
         <v>45620</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20832,7 +20832,7 @@
         <v>46052</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20905,7 +20905,7 @@
         <v>45246</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20978,7 +20978,7 @@
         <v>46059</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21051,7 +21051,7 @@
         <v>45926</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21124,7 +21124,7 @@
         <v>45595</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21197,7 +21197,7 @@
         <v>45996</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21270,7 +21270,7 @@
         <v>45996</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21343,7 +21343,7 @@
         <v>46171</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21416,7 +21416,7 @@
         <v>46176</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21489,7 +21489,7 @@
         <v>46191</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21562,7 +21562,7 @@
         <v>46191</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21635,7 +21635,7 @@
         <v>46191</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21708,7 +21708,7 @@
         <v>46203</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21781,7 +21781,7 @@
         <v>46202</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21854,7 +21854,7 @@
         <v>46203</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21927,7 +21927,7 @@
         <v>45316</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22000,7 +22000,7 @@
         <v>45594</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22073,7 +22073,7 @@
         <v>46216</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22146,7 +22146,7 @@
         <v>46268</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22219,7 +22219,7 @@
         <v>46267</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22292,7 +22292,7 @@
         <v>46267</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22365,7 +22365,7 @@
         <v>46268</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22438,7 +22438,7 @@
         <v>46232</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22511,7 +22511,7 @@
         <v>46273</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22589,7 +22589,7 @@
         <v>46273</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22667,7 +22667,7 @@
         <v>46244</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22740,7 +22740,7 @@
         <v>46246</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22813,7 +22813,7 @@
         <v>46251</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22886,7 +22886,7 @@
         <v>46254</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22959,7 +22959,7 @@
         <v>46246</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23032,7 +23032,7 @@
         <v>46268</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23105,7 +23105,7 @@
         <v>45712</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>45712</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23251,7 +23251,7 @@
         <v>45712</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23324,7 +23324,7 @@
         <v>45737</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>

--- a/Översikt HABO.xlsx
+++ b/Översikt HABO.xlsx
@@ -601,7 +601,7 @@
         <v>45337</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>44607</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
         <v>44749</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>45534</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>45635</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>45791</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>45183</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>44877</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>45882</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>44749</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>45534</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>45811</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>45631</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>45106</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>45419</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>44824</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>45225</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>45635</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>45930</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>44801</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>45882</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>45597</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>45747</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         <v>45635</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
         <v>45543</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         <v>45183</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         <v>45933</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>45813</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>44749</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>45635</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>45882</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>45985</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>44799</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>45355</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>44847</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>44527</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44769</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>44846</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>44693</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         <v>44877</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>44670</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>44500</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>44859</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>44693</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>44640</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         <v>45203</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>44623</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>44727</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         <v>44628</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5452,7 +5452,7 @@
         <v>45091</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>45698</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>45698</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>44749</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>44799</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>45218</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>45363</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>45236</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         <v>45641</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
         <v>45631</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>45558</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>45091</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>45091</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6401,7 +6401,7 @@
         <v>45099</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>45204</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>45636</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         <v>45120</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6693,7 +6693,7 @@
         <v>45750</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>44775</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>45595</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>45307</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
         <v>45478</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         <v>45390</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>45450</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>45450</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>45635</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7350,7 +7350,7 @@
         <v>45222</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7423,7 +7423,7 @@
         <v>45287</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7496,7 +7496,7 @@
         <v>45020</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7569,7 +7569,7 @@
         <v>45397</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7642,7 +7642,7 @@
         <v>45470</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>45372</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>44488</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7861,7 +7861,7 @@
         <v>45594</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         <v>45887</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>45882</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>44877</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>44951</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>45469</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>45620</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         <v>44939</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         <v>45475</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         <v>45896</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8596,7 +8596,7 @@
         <v>45217</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         <v>45029</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8742,7 +8742,7 @@
         <v>45903</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         <v>45635</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
         <v>45644</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         <v>45419</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9034,7 +9034,7 @@
         <v>45149</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9107,7 +9107,7 @@
         <v>45510</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         <v>45469</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>45475</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>45121</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         <v>45576</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9477,7 +9477,7 @@
         <v>45400</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>45597</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9628,7 +9628,7 @@
         <v>45646</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9701,7 +9701,7 @@
         <v>45602</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9774,7 +9774,7 @@
         <v>44488</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
         <v>44488</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9920,7 +9920,7 @@
         <v>45777</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9993,7 +9993,7 @@
         <v>45777</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10066,7 +10066,7 @@
         <v>45020</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10139,7 +10139,7 @@
         <v>45020</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>45099</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
         <v>45560</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
         <v>45638</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10431,7 +10431,7 @@
         <v>45677</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
         <v>44628</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10577,7 +10577,7 @@
         <v>45706</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10650,7 +10650,7 @@
         <v>45621</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10723,7 +10723,7 @@
         <v>45621</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10796,7 +10796,7 @@
         <v>45621</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10869,7 +10869,7 @@
         <v>45429</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
         <v>45922</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11015,7 +11015,7 @@
         <v>45789</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11088,7 +11088,7 @@
         <v>45922</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11161,7 +11161,7 @@
         <v>45580</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11234,7 +11234,7 @@
         <v>45119</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11307,7 +11307,7 @@
         <v>45119</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11380,7 +11380,7 @@
         <v>45356</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11453,7 +11453,7 @@
         <v>45671</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11526,7 +11526,7 @@
         <v>45576</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11599,7 +11599,7 @@
         <v>45926</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11672,7 +11672,7 @@
         <v>45621</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11745,7 +11745,7 @@
         <v>45636</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
         <v>45608</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11891,7 +11891,7 @@
         <v>45111</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11964,7 +11964,7 @@
         <v>44571</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12037,7 +12037,7 @@
         <v>45931</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12110,7 +12110,7 @@
         <v>45595</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12183,7 +12183,7 @@
         <v>45595</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12256,7 +12256,7 @@
         <v>44749</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
         <v>45450</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12402,7 +12402,7 @@
         <v>45106</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12475,7 +12475,7 @@
         <v>45021</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12548,7 +12548,7 @@
         <v>44995</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12621,7 +12621,7 @@
         <v>45364</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12694,7 +12694,7 @@
         <v>45734</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         <v>45210</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12840,7 +12840,7 @@
         <v>45554</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12913,7 +12913,7 @@
         <v>45617</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12986,7 +12986,7 @@
         <v>45638</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13059,7 +13059,7 @@
         <v>44783</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13137,7 +13137,7 @@
         <v>45597</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         <v>45099</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13288,7 +13288,7 @@
         <v>44914</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>44816</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13434,7 +13434,7 @@
         <v>45807</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13507,7 +13507,7 @@
         <v>45733</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13580,7 +13580,7 @@
         <v>45687</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13653,7 +13653,7 @@
         <v>45812</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13726,7 +13726,7 @@
         <v>45220</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13799,7 +13799,7 @@
         <v>45597</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13877,7 +13877,7 @@
         <v>45620</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13950,7 +13950,7 @@
         <v>45810</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14023,7 +14023,7 @@
         <v>45152</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14096,7 +14096,7 @@
         <v>45120</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14169,7 +14169,7 @@
         <v>45950</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14242,7 +14242,7 @@
         <v>45107</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14315,7 +14315,7 @@
         <v>45811</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14388,7 +14388,7 @@
         <v>45120</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14461,7 +14461,7 @@
         <v>45951</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14534,7 +14534,7 @@
         <v>44488</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14607,7 +14607,7 @@
         <v>45827</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14680,7 +14680,7 @@
         <v>45827</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14753,7 +14753,7 @@
         <v>45183</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14826,7 +14826,7 @@
         <v>45188</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14899,7 +14899,7 @@
         <v>45972</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14972,7 +14972,7 @@
         <v>45760</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15045,7 +15045,7 @@
         <v>45119</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15118,7 +15118,7 @@
         <v>45119</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15191,7 +15191,7 @@
         <v>45120</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15264,7 +15264,7 @@
         <v>45974</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15337,7 +15337,7 @@
         <v>45846</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15410,7 +15410,7 @@
         <v>45734</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15483,7 +15483,7 @@
         <v>45242</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15561,7 +15561,7 @@
         <v>45475</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15634,7 +15634,7 @@
         <v>45475</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15707,7 +15707,7 @@
         <v>45146</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15780,7 +15780,7 @@
         <v>45810</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15853,7 +15853,7 @@
         <v>45660</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15926,7 +15926,7 @@
         <v>45647</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>45478</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16072,7 +16072,7 @@
         <v>45450</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16145,7 +16145,7 @@
         <v>45450</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16218,7 +16218,7 @@
         <v>45751</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16291,7 +16291,7 @@
         <v>45698</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>45687</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16437,7 +16437,7 @@
         <v>45212</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16510,7 +16510,7 @@
         <v>45877</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16583,7 +16583,7 @@
         <v>45757</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16656,7 +16656,7 @@
         <v>45757</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16729,7 +16729,7 @@
         <v>45271</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16802,7 +16802,7 @@
         <v>45111</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16875,7 +16875,7 @@
         <v>45882</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16948,7 +16948,7 @@
         <v>45621</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17021,7 +17021,7 @@
         <v>45621</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17094,7 +17094,7 @@
         <v>45882</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17172,7 +17172,7 @@
         <v>45882</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17245,7 +17245,7 @@
         <v>45113</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>44830</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17391,7 +17391,7 @@
         <v>45278</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17464,7 +17464,7 @@
         <v>45007</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17537,7 +17537,7 @@
         <v>45985</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         <v>45985</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17693,7 +17693,7 @@
         <v>45751</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17766,7 +17766,7 @@
         <v>44896</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17839,7 +17839,7 @@
         <v>45173</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17912,7 +17912,7 @@
         <v>44876</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17985,7 +17985,7 @@
         <v>45982</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>44845</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18131,7 +18131,7 @@
         <v>44894</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18204,7 +18204,7 @@
         <v>45620</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18277,7 +18277,7 @@
         <v>44575</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18350,7 +18350,7 @@
         <v>44909</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18423,7 +18423,7 @@
         <v>46000</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18496,7 +18496,7 @@
         <v>45030</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18569,7 +18569,7 @@
         <v>44801</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18642,7 +18642,7 @@
         <v>46000</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>46000</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>45271</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18861,7 +18861,7 @@
         <v>46000</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>46135</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19007,7 +19007,7 @@
         <v>44749</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19080,7 +19080,7 @@
         <v>44749</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19153,7 +19153,7 @@
         <v>44995</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>45595</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19299,7 +19299,7 @@
         <v>44797</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19372,7 +19372,7 @@
         <v>44944</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19445,7 +19445,7 @@
         <v>45152</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19518,7 +19518,7 @@
         <v>45698</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19591,7 +19591,7 @@
         <v>44913</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>45820</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19737,7 +19737,7 @@
         <v>46037</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19810,7 +19810,7 @@
         <v>46037</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19883,7 +19883,7 @@
         <v>46037</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
         <v>46041</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>46043</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20102,7 +20102,7 @@
         <v>46043</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20175,7 +20175,7 @@
         <v>46043</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20248,7 +20248,7 @@
         <v>46043</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20321,7 +20321,7 @@
         <v>46043</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20394,7 +20394,7 @@
         <v>46043</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20467,7 +20467,7 @@
         <v>45030</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20540,7 +20540,7 @@
         <v>45120</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20613,7 +20613,7 @@
         <v>45120</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20686,7 +20686,7 @@
         <v>45400</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20759,7 +20759,7 @@
         <v>45620</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20832,7 +20832,7 @@
         <v>46052</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20905,7 +20905,7 @@
         <v>45246</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20978,7 +20978,7 @@
         <v>46059</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21051,7 +21051,7 @@
         <v>45926</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21124,7 +21124,7 @@
         <v>45595</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21197,7 +21197,7 @@
         <v>45996</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21270,7 +21270,7 @@
         <v>45996</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21343,7 +21343,7 @@
         <v>46171</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21416,7 +21416,7 @@
         <v>46176</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21489,7 +21489,7 @@
         <v>46191</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21562,7 +21562,7 @@
         <v>46191</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21635,7 +21635,7 @@
         <v>46191</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21708,7 +21708,7 @@
         <v>46203</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21781,7 +21781,7 @@
         <v>46202</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21854,7 +21854,7 @@
         <v>46203</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21927,7 +21927,7 @@
         <v>45316</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22000,7 +22000,7 @@
         <v>45594</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22073,7 +22073,7 @@
         <v>46216</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22146,7 +22146,7 @@
         <v>46268</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22219,7 +22219,7 @@
         <v>46267</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22292,7 +22292,7 @@
         <v>46267</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22365,7 +22365,7 @@
         <v>46268</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22438,7 +22438,7 @@
         <v>46232</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22511,7 +22511,7 @@
         <v>46273</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22589,7 +22589,7 @@
         <v>46273</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22667,7 +22667,7 @@
         <v>46244</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22740,7 +22740,7 @@
         <v>46246</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22813,7 +22813,7 @@
         <v>46251</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22886,7 +22886,7 @@
         <v>46254</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22959,7 +22959,7 @@
         <v>46246</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23032,7 +23032,7 @@
         <v>46268</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23105,7 +23105,7 @@
         <v>45712</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>45712</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23251,7 +23251,7 @@
         <v>45712</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23324,7 +23324,7 @@
         <v>45737</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>

--- a/Översikt HABO.xlsx
+++ b/Översikt HABO.xlsx
@@ -601,7 +601,7 @@
         <v>45337</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>44607</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
         <v>44749</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>45534</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>45183</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>45635</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>45791</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>44877</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>45882</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>44749</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>45419</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>45534</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>45106</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>45631</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>45811</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>44824</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>45930</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>45225</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>44801</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>45635</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>45882</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>45543</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>44749</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>45597</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         <v>45933</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>45635</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>45985</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>45747</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>44799</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>45635</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>45183</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4027,7 +4027,7 @@
         <v>45813</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>45882</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>45355</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>44847</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>44527</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44769</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>44846</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>44693</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         <v>44877</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>44693</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>44640</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>44670</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>44859</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>44727</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         <v>44500</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>44623</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>45475</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         <v>45212</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5452,7 +5452,7 @@
         <v>45029</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>45091</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>45660</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>45641</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>45698</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>45636</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>45687</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>44801</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         <v>45111</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
         <v>45478</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>45620</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>45621</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>45621</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6401,7 +6401,7 @@
         <v>45621</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>44571</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>45475</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         <v>45475</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6693,7 +6693,7 @@
         <v>45120</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>45146</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>45602</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>45597</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         <v>45030</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>44783</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>45621</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>45030</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7287,7 +7287,7 @@
         <v>45210</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         <v>45278</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>45595</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>45595</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>44951</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>45475</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         <v>45621</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         <v>45621</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7871,7 +7871,7 @@
         <v>44896</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7944,7 +7944,7 @@
         <v>45597</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8022,7 +8022,7 @@
         <v>45560</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         <v>45107</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8168,7 +8168,7 @@
         <v>44799</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
         <v>45121</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8314,7 +8314,7 @@
         <v>45149</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>44749</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>44749</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         <v>45635</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>45111</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>45091</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>45646</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8825,7 +8825,7 @@
         <v>45671</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
         <v>45099</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>45099</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         <v>45469</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         <v>45882</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9190,7 +9190,7 @@
         <v>45887</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         <v>44816</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9336,7 +9336,7 @@
         <v>44845</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9409,7 +9409,7 @@
         <v>45820</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9482,7 +9482,7 @@
         <v>45882</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>45896</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9633,7 +9633,7 @@
         <v>44488</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9706,7 +9706,7 @@
         <v>45760</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9779,7 +9779,7 @@
         <v>45903</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
         <v>45246</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         <v>44944</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9998,7 +9998,7 @@
         <v>45922</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10071,7 +10071,7 @@
         <v>45620</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10144,7 +10144,7 @@
         <v>44628</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10217,7 +10217,7 @@
         <v>45922</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10290,7 +10290,7 @@
         <v>44575</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10363,7 +10363,7 @@
         <v>45020</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10436,7 +10436,7 @@
         <v>45020</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10509,7 +10509,7 @@
         <v>45926</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10582,7 +10582,7 @@
         <v>45931</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10655,7 +10655,7 @@
         <v>45222</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
         <v>45173</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10801,7 +10801,7 @@
         <v>45558</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>44894</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10947,7 +10947,7 @@
         <v>45950</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>45951</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11093,7 +11093,7 @@
         <v>45469</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11171,7 +11171,7 @@
         <v>45926</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11244,7 +11244,7 @@
         <v>44749</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11317,7 +11317,7 @@
         <v>44749</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11390,7 +11390,7 @@
         <v>45751</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>44628</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         <v>45099</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11609,7 +11609,7 @@
         <v>45429</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11682,7 +11682,7 @@
         <v>45400</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11755,7 +11755,7 @@
         <v>45188</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
         <v>45972</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11901,7 +11901,7 @@
         <v>45974</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11974,7 +11974,7 @@
         <v>45450</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12047,7 +12047,7 @@
         <v>45597</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12125,7 +12125,7 @@
         <v>45706</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12198,7 +12198,7 @@
         <v>45595</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12271,7 +12271,7 @@
         <v>45120</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12344,7 +12344,7 @@
         <v>45985</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12422,7 +12422,7 @@
         <v>45985</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>45982</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12573,7 +12573,7 @@
         <v>45478</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12646,7 +12646,7 @@
         <v>45020</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12719,7 +12719,7 @@
         <v>45996</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12792,7 +12792,7 @@
         <v>45698</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12865,7 +12865,7 @@
         <v>45698</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12938,7 +12938,7 @@
         <v>45996</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13011,7 +13011,7 @@
         <v>46000</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13084,7 +13084,7 @@
         <v>46000</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
         <v>46000</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>46000</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>46171</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>44797</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13449,7 +13449,7 @@
         <v>44913</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>45287</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13595,7 +13595,7 @@
         <v>45419</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13668,7 +13668,7 @@
         <v>45617</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13741,7 +13741,7 @@
         <v>45750</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>45271</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13887,7 +13887,7 @@
         <v>45638</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
         <v>46176</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14033,7 +14033,7 @@
         <v>46037</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>46037</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14179,7 +14179,7 @@
         <v>46037</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14252,7 +14252,7 @@
         <v>46041</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14325,7 +14325,7 @@
         <v>46043</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14398,7 +14398,7 @@
         <v>46043</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14471,7 +14471,7 @@
         <v>46043</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14544,7 +14544,7 @@
         <v>46043</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14617,7 +14617,7 @@
         <v>46043</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14690,7 +14690,7 @@
         <v>46043</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14763,7 +14763,7 @@
         <v>45450</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14836,7 +14836,7 @@
         <v>45450</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>45576</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14982,7 +14982,7 @@
         <v>45183</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15055,7 +15055,7 @@
         <v>46052</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>46059</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15201,7 +15201,7 @@
         <v>45271</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15274,7 +15274,7 @@
         <v>44876</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15347,7 +15347,7 @@
         <v>45242</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15425,7 +15425,7 @@
         <v>44830</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15498,7 +15498,7 @@
         <v>45677</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15571,7 +15571,7 @@
         <v>45218</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15644,7 +15644,7 @@
         <v>45203</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>45638</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15790,7 +15790,7 @@
         <v>46191</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15863,7 +15863,7 @@
         <v>46191</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>45733</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16009,7 +16009,7 @@
         <v>46191</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16082,7 +16082,7 @@
         <v>45594</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16155,7 +16155,7 @@
         <v>45595</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16228,7 +16228,7 @@
         <v>45470</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>45620</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16374,7 +16374,7 @@
         <v>45620</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16447,7 +16447,7 @@
         <v>45450</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16520,7 +16520,7 @@
         <v>45450</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16593,7 +16593,7 @@
         <v>45400</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16666,7 +16666,7 @@
         <v>46203</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16739,7 +16739,7 @@
         <v>45734</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16812,7 +16812,7 @@
         <v>46203</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16885,7 +16885,7 @@
         <v>46135</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16958,7 +16958,7 @@
         <v>46202</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17031,7 +17031,7 @@
         <v>45113</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17104,7 +17104,7 @@
         <v>45698</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17177,7 +17177,7 @@
         <v>45554</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17250,7 +17250,7 @@
         <v>45236</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>45220</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17396,7 +17396,7 @@
         <v>45356</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17469,7 +17469,7 @@
         <v>45316</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>45594</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         <v>46216</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>44939</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17761,7 +17761,7 @@
         <v>44995</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17834,7 +17834,7 @@
         <v>45091</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17907,7 +17907,7 @@
         <v>44877</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17980,7 +17980,7 @@
         <v>45397</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18053,7 +18053,7 @@
         <v>45307</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>46273</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18204,7 +18204,7 @@
         <v>45580</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18277,7 +18277,7 @@
         <v>45007</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18350,7 +18350,7 @@
         <v>46273</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18428,7 +18428,7 @@
         <v>45152</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18501,7 +18501,7 @@
         <v>45510</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18574,7 +18574,7 @@
         <v>45576</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18647,7 +18647,7 @@
         <v>45635</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18720,7 +18720,7 @@
         <v>46232</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18793,7 +18793,7 @@
         <v>45757</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18866,7 +18866,7 @@
         <v>45757</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18939,7 +18939,7 @@
         <v>45204</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19012,7 +19012,7 @@
         <v>45595</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19085,7 +19085,7 @@
         <v>45390</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19158,7 +19158,7 @@
         <v>45631</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19231,7 +19231,7 @@
         <v>44909</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>45372</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19377,7 +19377,7 @@
         <v>45647</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19450,7 +19450,7 @@
         <v>44488</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19523,7 +19523,7 @@
         <v>46244</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19596,7 +19596,7 @@
         <v>45636</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19669,7 +19669,7 @@
         <v>46246</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19742,7 +19742,7 @@
         <v>45644</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19815,7 +19815,7 @@
         <v>45120</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19888,7 +19888,7 @@
         <v>45119</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19961,7 +19961,7 @@
         <v>45119</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20034,7 +20034,7 @@
         <v>44488</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20107,7 +20107,7 @@
         <v>44488</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20180,7 +20180,7 @@
         <v>45119</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20253,7 +20253,7 @@
         <v>45152</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20326,7 +20326,7 @@
         <v>44995</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20399,7 +20399,7 @@
         <v>45363</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20472,7 +20472,7 @@
         <v>44914</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20545,7 +20545,7 @@
         <v>46251</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20618,7 +20618,7 @@
         <v>45217</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20691,7 +20691,7 @@
         <v>45106</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20764,7 +20764,7 @@
         <v>45119</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20837,7 +20837,7 @@
         <v>45120</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>45120</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20983,7 +20983,7 @@
         <v>45120</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21056,7 +21056,7 @@
         <v>45687</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21129,7 +21129,7 @@
         <v>46254</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21202,7 +21202,7 @@
         <v>44775</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21275,7 +21275,7 @@
         <v>46246</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
         <v>45777</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21421,7 +21421,7 @@
         <v>45777</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21494,7 +21494,7 @@
         <v>45789</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21567,7 +21567,7 @@
         <v>45608</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>45364</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21713,7 +21713,7 @@
         <v>45021</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21786,7 +21786,7 @@
         <v>45734</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21859,7 +21859,7 @@
         <v>45807</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21932,7 +21932,7 @@
         <v>45810</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22005,7 +22005,7 @@
         <v>46268</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22078,7 +22078,7 @@
         <v>45812</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22151,7 +22151,7 @@
         <v>46267</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22224,7 +22224,7 @@
         <v>46267</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22297,7 +22297,7 @@
         <v>45811</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22370,7 +22370,7 @@
         <v>46310</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22443,7 +22443,7 @@
         <v>45827</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22516,7 +22516,7 @@
         <v>46268</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22589,7 +22589,7 @@
         <v>45827</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22662,7 +22662,7 @@
         <v>46268</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22735,7 +22735,7 @@
         <v>45846</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22808,7 +22808,7 @@
         <v>45810</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22881,7 +22881,7 @@
         <v>45751</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22954,7 +22954,7 @@
         <v>45877</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23027,7 +23027,7 @@
         <v>45882</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23105,7 +23105,7 @@
         <v>45882</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>45712</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23251,7 +23251,7 @@
         <v>45712</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23324,7 +23324,7 @@
         <v>45712</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>45737</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>

--- a/Översikt HABO.xlsx
+++ b/Översikt HABO.xlsx
@@ -601,7 +601,7 @@
         <v>45337</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>44607</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
         <v>44749</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>45534</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>45183</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>45635</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>45791</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>44877</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>45882</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>44749</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>45419</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>45534</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>45106</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>45631</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>45811</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>44824</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>45930</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>45225</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>44801</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>45635</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>45882</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>45543</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>44749</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>45597</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         <v>45933</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>45635</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>45985</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>45747</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>44799</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>45635</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>45183</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4027,7 +4027,7 @@
         <v>45813</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>45882</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>45355</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>44847</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>44527</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44769</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>44846</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>44693</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         <v>44877</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>44693</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>44640</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>44670</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>44859</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>44727</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         <v>44500</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>44623</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>45475</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         <v>45212</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5452,7 +5452,7 @@
         <v>45029</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>45091</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>45660</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>45641</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>45698</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>45636</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>45687</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>44801</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         <v>45111</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
         <v>45478</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>45620</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>45621</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>45621</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6401,7 +6401,7 @@
         <v>45621</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>44571</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>45475</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         <v>45475</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6693,7 +6693,7 @@
         <v>45120</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>45146</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>45602</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>45597</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         <v>45030</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>44783</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>45621</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>45030</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7287,7 +7287,7 @@
         <v>45210</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         <v>45278</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>45595</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>45595</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>44951</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>45475</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         <v>45621</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         <v>45621</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7871,7 +7871,7 @@
         <v>44896</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7944,7 +7944,7 @@
         <v>45597</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8022,7 +8022,7 @@
         <v>45560</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         <v>45107</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8168,7 +8168,7 @@
         <v>44799</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
         <v>45121</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8314,7 +8314,7 @@
         <v>45149</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>44749</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>44749</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         <v>45635</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>45111</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>45091</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>45646</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8825,7 +8825,7 @@
         <v>45671</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
         <v>45099</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>45099</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         <v>45469</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         <v>45882</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9190,7 +9190,7 @@
         <v>45887</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         <v>44816</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9336,7 +9336,7 @@
         <v>44845</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9409,7 +9409,7 @@
         <v>45820</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9482,7 +9482,7 @@
         <v>45882</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>45896</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9633,7 +9633,7 @@
         <v>44488</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9706,7 +9706,7 @@
         <v>45760</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9779,7 +9779,7 @@
         <v>45903</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
         <v>45246</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         <v>44944</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9998,7 +9998,7 @@
         <v>45922</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10071,7 +10071,7 @@
         <v>45620</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10144,7 +10144,7 @@
         <v>44628</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10217,7 +10217,7 @@
         <v>45922</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10290,7 +10290,7 @@
         <v>44575</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10363,7 +10363,7 @@
         <v>45020</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10436,7 +10436,7 @@
         <v>45020</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10509,7 +10509,7 @@
         <v>45926</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10582,7 +10582,7 @@
         <v>45931</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10655,7 +10655,7 @@
         <v>45222</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
         <v>45173</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10801,7 +10801,7 @@
         <v>45558</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>44894</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10947,7 +10947,7 @@
         <v>45950</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>45951</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11093,7 +11093,7 @@
         <v>45469</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11171,7 +11171,7 @@
         <v>45926</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11244,7 +11244,7 @@
         <v>44749</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11317,7 +11317,7 @@
         <v>44749</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11390,7 +11390,7 @@
         <v>45751</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>44628</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         <v>45099</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11609,7 +11609,7 @@
         <v>45429</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11682,7 +11682,7 @@
         <v>45400</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11755,7 +11755,7 @@
         <v>45188</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
         <v>45972</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11901,7 +11901,7 @@
         <v>45974</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11974,7 +11974,7 @@
         <v>45450</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12047,7 +12047,7 @@
         <v>45597</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12125,7 +12125,7 @@
         <v>45706</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12198,7 +12198,7 @@
         <v>45595</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12271,7 +12271,7 @@
         <v>45120</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12344,7 +12344,7 @@
         <v>45985</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12422,7 +12422,7 @@
         <v>45985</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>45982</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12573,7 +12573,7 @@
         <v>45478</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12646,7 +12646,7 @@
         <v>45020</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12719,7 +12719,7 @@
         <v>45996</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12792,7 +12792,7 @@
         <v>45698</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12865,7 +12865,7 @@
         <v>45698</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12938,7 +12938,7 @@
         <v>45996</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13011,7 +13011,7 @@
         <v>46000</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13084,7 +13084,7 @@
         <v>46000</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
         <v>46000</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>46000</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>46171</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>44797</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13449,7 +13449,7 @@
         <v>44913</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>45287</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13595,7 +13595,7 @@
         <v>45419</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13668,7 +13668,7 @@
         <v>45617</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13741,7 +13741,7 @@
         <v>45750</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>45271</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13887,7 +13887,7 @@
         <v>45638</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
         <v>46176</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14033,7 +14033,7 @@
         <v>46037</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>46037</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14179,7 +14179,7 @@
         <v>46037</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14252,7 +14252,7 @@
         <v>46041</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14325,7 +14325,7 @@
         <v>46043</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14398,7 +14398,7 @@
         <v>46043</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14471,7 +14471,7 @@
         <v>46043</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14544,7 +14544,7 @@
         <v>46043</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14617,7 +14617,7 @@
         <v>46043</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14690,7 +14690,7 @@
         <v>46043</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14763,7 +14763,7 @@
         <v>45450</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14836,7 +14836,7 @@
         <v>45450</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>45576</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14982,7 +14982,7 @@
         <v>45183</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15055,7 +15055,7 @@
         <v>46052</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>46059</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15201,7 +15201,7 @@
         <v>45271</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15274,7 +15274,7 @@
         <v>44876</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15347,7 +15347,7 @@
         <v>45242</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15425,7 +15425,7 @@
         <v>44830</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15498,7 +15498,7 @@
         <v>45677</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15571,7 +15571,7 @@
         <v>45218</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15644,7 +15644,7 @@
         <v>45203</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>45638</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15790,7 +15790,7 @@
         <v>46191</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15863,7 +15863,7 @@
         <v>46191</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>45733</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16009,7 +16009,7 @@
         <v>46191</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16082,7 +16082,7 @@
         <v>45594</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16155,7 +16155,7 @@
         <v>45595</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16228,7 +16228,7 @@
         <v>45470</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>45620</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16374,7 +16374,7 @@
         <v>45620</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16447,7 +16447,7 @@
         <v>45450</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16520,7 +16520,7 @@
         <v>45450</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16593,7 +16593,7 @@
         <v>45400</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16666,7 +16666,7 @@
         <v>46203</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16739,7 +16739,7 @@
         <v>45734</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16812,7 +16812,7 @@
         <v>46203</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16885,7 +16885,7 @@
         <v>46135</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16958,7 +16958,7 @@
         <v>46202</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17031,7 +17031,7 @@
         <v>45113</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17104,7 +17104,7 @@
         <v>45698</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17177,7 +17177,7 @@
         <v>45554</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17250,7 +17250,7 @@
         <v>45236</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>45220</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17396,7 +17396,7 @@
         <v>45356</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17469,7 +17469,7 @@
         <v>45316</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>45594</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         <v>46216</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>44939</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17761,7 +17761,7 @@
         <v>44995</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17834,7 +17834,7 @@
         <v>45091</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17907,7 +17907,7 @@
         <v>44877</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17980,7 +17980,7 @@
         <v>45397</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18053,7 +18053,7 @@
         <v>45307</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>46273</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18204,7 +18204,7 @@
         <v>45580</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18277,7 +18277,7 @@
         <v>45007</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18350,7 +18350,7 @@
         <v>46273</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18428,7 +18428,7 @@
         <v>45152</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18501,7 +18501,7 @@
         <v>45510</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18574,7 +18574,7 @@
         <v>45576</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18647,7 +18647,7 @@
         <v>45635</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18720,7 +18720,7 @@
         <v>46232</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18793,7 +18793,7 @@
         <v>45757</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18866,7 +18866,7 @@
         <v>45757</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18939,7 +18939,7 @@
         <v>45204</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19012,7 +19012,7 @@
         <v>45595</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19085,7 +19085,7 @@
         <v>45390</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19158,7 +19158,7 @@
         <v>45631</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19231,7 +19231,7 @@
         <v>44909</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>45372</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19377,7 +19377,7 @@
         <v>45647</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19450,7 +19450,7 @@
         <v>44488</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19523,7 +19523,7 @@
         <v>46244</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19596,7 +19596,7 @@
         <v>45636</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19669,7 +19669,7 @@
         <v>46246</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19742,7 +19742,7 @@
         <v>45644</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19815,7 +19815,7 @@
         <v>45120</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19888,7 +19888,7 @@
         <v>45119</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19961,7 +19961,7 @@
         <v>45119</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20034,7 +20034,7 @@
         <v>44488</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20107,7 +20107,7 @@
         <v>44488</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20180,7 +20180,7 @@
         <v>45119</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20253,7 +20253,7 @@
         <v>45152</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20326,7 +20326,7 @@
         <v>44995</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20399,7 +20399,7 @@
         <v>45363</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20472,7 +20472,7 @@
         <v>44914</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20545,7 +20545,7 @@
         <v>46251</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20618,7 +20618,7 @@
         <v>45217</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20691,7 +20691,7 @@
         <v>45106</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20764,7 +20764,7 @@
         <v>45119</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20837,7 +20837,7 @@
         <v>45120</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>45120</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20983,7 +20983,7 @@
         <v>45120</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21056,7 +21056,7 @@
         <v>45687</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21129,7 +21129,7 @@
         <v>46254</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21202,7 +21202,7 @@
         <v>44775</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21275,7 +21275,7 @@
         <v>46246</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
         <v>45777</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21421,7 +21421,7 @@
         <v>45777</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21494,7 +21494,7 @@
         <v>45789</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21567,7 +21567,7 @@
         <v>45608</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>45364</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21713,7 +21713,7 @@
         <v>45021</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21786,7 +21786,7 @@
         <v>45734</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21859,7 +21859,7 @@
         <v>45807</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21932,7 +21932,7 @@
         <v>45810</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22005,7 +22005,7 @@
         <v>46268</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22078,7 +22078,7 @@
         <v>45812</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22151,7 +22151,7 @@
         <v>46267</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22224,7 +22224,7 @@
         <v>46267</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22297,7 +22297,7 @@
         <v>45811</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22370,7 +22370,7 @@
         <v>46310</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22443,7 +22443,7 @@
         <v>45827</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22516,7 +22516,7 @@
         <v>46268</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22589,7 +22589,7 @@
         <v>45827</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22662,7 +22662,7 @@
         <v>46268</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22735,7 +22735,7 @@
         <v>45846</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22808,7 +22808,7 @@
         <v>45810</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22881,7 +22881,7 @@
         <v>45751</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22954,7 +22954,7 @@
         <v>45877</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23027,7 +23027,7 @@
         <v>45882</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23105,7 +23105,7 @@
         <v>45882</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>45712</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23251,7 +23251,7 @@
         <v>45712</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23324,7 +23324,7 @@
         <v>45712</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>45737</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>

--- a/Översikt HABO.xlsx
+++ b/Översikt HABO.xlsx
@@ -601,7 +601,7 @@
         <v>45337</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>44607</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
         <v>44749</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>45534</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>45791</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45635</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>45183</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>45882</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>44877</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>45106</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>45419</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>44749</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>45811</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>45534</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>45631</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>44824</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>45930</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>45225</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>45635</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>45882</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>44801</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>45933</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>45985</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         <v>45597</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>45747</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>45813</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         <v>45882</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>45543</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>45635</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>45635</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>45183</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4027,7 +4027,7 @@
         <v>44749</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>44799</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>45355</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>44847</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>44527</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44769</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>44846</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>44693</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         <v>44877</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>44693</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>44640</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>44670</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>44859</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>44727</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         <v>44500</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>44623</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>45887</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         <v>45882</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         <v>44799</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         <v>44749</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5603,7 +5603,7 @@
         <v>44749</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>45896</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5749,7 +5749,7 @@
         <v>44995</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>45203</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         <v>45595</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>45903</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         <v>44797</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>44944</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>45152</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>45595</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         <v>44913</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>45996</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         <v>45922</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6552,7 +6552,7 @@
         <v>45996</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6625,7 +6625,7 @@
         <v>45922</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         <v>45698</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>45926</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>45698</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>45931</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         <v>45030</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>45120</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7136,7 +7136,7 @@
         <v>45120</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>46171</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         <v>45218</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>45363</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>45400</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
         <v>45620</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>44628</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>46176</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>45478</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         <v>45390</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>45450</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         <v>45450</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>45641</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>45950</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>45091</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>45091</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>45951</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         <v>45204</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         <v>45750</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         <v>44775</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8596,7 +8596,7 @@
         <v>45595</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         <v>45307</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8742,7 +8742,7 @@
         <v>45635</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         <v>46191</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
         <v>45222</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         <v>46191</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9034,7 +9034,7 @@
         <v>46191</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9107,7 +9107,7 @@
         <v>45972</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         <v>45974</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>45470</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9326,7 +9326,7 @@
         <v>45372</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
         <v>46203</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9472,7 +9472,7 @@
         <v>46202</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         <v>44877</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9618,7 +9618,7 @@
         <v>46203</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9691,7 +9691,7 @@
         <v>45985</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9769,7 +9769,7 @@
         <v>45985</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
         <v>45475</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9920,7 +9920,7 @@
         <v>45982</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9993,7 +9993,7 @@
         <v>45217</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10066,7 +10066,7 @@
         <v>45316</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10139,7 +10139,7 @@
         <v>45594</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>45644</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
         <v>45594</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
         <v>46216</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10431,7 +10431,7 @@
         <v>45469</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10509,7 +10509,7 @@
         <v>45400</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10582,7 +10582,7 @@
         <v>46000</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10655,7 +10655,7 @@
         <v>46000</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
         <v>46000</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10801,7 +10801,7 @@
         <v>45777</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>45777</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10947,7 +10947,7 @@
         <v>46000</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>46232</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11093,7 +11093,7 @@
         <v>45789</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11166,7 +11166,7 @@
         <v>45608</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11239,7 +11239,7 @@
         <v>46037</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11312,7 +11312,7 @@
         <v>46037</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11385,7 +11385,7 @@
         <v>46037</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11458,7 +11458,7 @@
         <v>46041</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         <v>46244</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         <v>46043</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>46043</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11750,7 +11750,7 @@
         <v>45021</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11823,7 +11823,7 @@
         <v>46043</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11896,7 +11896,7 @@
         <v>46043</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11969,7 +11969,7 @@
         <v>46043</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12042,7 +12042,7 @@
         <v>46043</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12115,7 +12115,7 @@
         <v>45364</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12188,7 +12188,7 @@
         <v>45734</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
         <v>46052</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12334,7 +12334,7 @@
         <v>46246</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12407,7 +12407,7 @@
         <v>45807</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>46059</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
         <v>45812</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
         <v>45810</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12699,7 +12699,7 @@
         <v>45469</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>45811</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12845,7 +12845,7 @@
         <v>46251</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12918,7 +12918,7 @@
         <v>45827</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12991,7 +12991,7 @@
         <v>45827</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13064,7 +13064,7 @@
         <v>45620</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13137,7 +13137,7 @@
         <v>46254</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13210,7 +13210,7 @@
         <v>44939</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
         <v>46246</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13356,7 +13356,7 @@
         <v>45846</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13429,7 +13429,7 @@
         <v>45810</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13502,7 +13502,7 @@
         <v>45635</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13575,7 +13575,7 @@
         <v>45751</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13648,7 +13648,7 @@
         <v>45877</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13721,7 +13721,7 @@
         <v>45882</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13794,7 +13794,7 @@
         <v>45882</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13872,7 +13872,7 @@
         <v>45882</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>45597</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14023,7 +14023,7 @@
         <v>45646</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14096,7 +14096,7 @@
         <v>46135</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14169,7 +14169,7 @@
         <v>45560</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14242,7 +14242,7 @@
         <v>45677</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14315,7 +14315,7 @@
         <v>44628</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14388,7 +14388,7 @@
         <v>46267</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14461,7 +14461,7 @@
         <v>46267</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14534,7 +14534,7 @@
         <v>46310</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14607,7 +14607,7 @@
         <v>45698</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14680,7 +14680,7 @@
         <v>45820</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14753,7 +14753,7 @@
         <v>46268</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14826,7 +14826,7 @@
         <v>45671</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14899,7 +14899,7 @@
         <v>46268</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14972,7 +14972,7 @@
         <v>46268</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15045,7 +15045,7 @@
         <v>45636</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15118,7 +15118,7 @@
         <v>46273</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>46273</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15274,7 +15274,7 @@
         <v>46315</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15352,7 +15352,7 @@
         <v>45595</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15425,7 +15425,7 @@
         <v>45595</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15498,7 +15498,7 @@
         <v>44749</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15571,7 +15571,7 @@
         <v>44995</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15644,7 +15644,7 @@
         <v>45246</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>45210</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15790,7 +15790,7 @@
         <v>45554</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15863,7 +15863,7 @@
         <v>44914</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>44816</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16009,7 +16009,7 @@
         <v>45733</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16082,7 +16082,7 @@
         <v>45597</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16160,7 +16160,7 @@
         <v>45926</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16233,7 +16233,7 @@
         <v>45107</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16306,7 +16306,7 @@
         <v>45119</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16379,7 +16379,7 @@
         <v>45119</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16452,7 +16452,7 @@
         <v>45120</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>45146</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16598,7 +16598,7 @@
         <v>45660</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16671,7 +16671,7 @@
         <v>45647</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16744,7 +16744,7 @@
         <v>45478</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16817,7 +16817,7 @@
         <v>45450</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16890,7 +16890,7 @@
         <v>45450</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16963,7 +16963,7 @@
         <v>45698</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17036,7 +17036,7 @@
         <v>45687</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17109,7 +17109,7 @@
         <v>45757</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17182,7 +17182,7 @@
         <v>45757</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17255,7 +17255,7 @@
         <v>45111</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17328,7 +17328,7 @@
         <v>45621</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17401,7 +17401,7 @@
         <v>45621</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17474,7 +17474,7 @@
         <v>45113</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         <v>44830</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17620,7 +17620,7 @@
         <v>45007</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17693,7 +17693,7 @@
         <v>45751</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17766,7 +17766,7 @@
         <v>45173</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17839,7 +17839,7 @@
         <v>44876</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17912,7 +17912,7 @@
         <v>44845</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17985,7 +17985,7 @@
         <v>44894</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>45620</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18131,7 +18131,7 @@
         <v>45091</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18204,7 +18204,7 @@
         <v>44749</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18277,7 +18277,7 @@
         <v>45236</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18350,7 +18350,7 @@
         <v>45631</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18423,7 +18423,7 @@
         <v>45558</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18496,7 +18496,7 @@
         <v>45099</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18569,7 +18569,7 @@
         <v>45636</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18642,7 +18642,7 @@
         <v>45120</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>45287</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>45020</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18861,7 +18861,7 @@
         <v>45397</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>44951</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19007,7 +19007,7 @@
         <v>45029</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19080,7 +19080,7 @@
         <v>45419</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19153,7 +19153,7 @@
         <v>45149</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>45510</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19299,7 +19299,7 @@
         <v>45475</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19372,7 +19372,7 @@
         <v>45121</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19445,7 +19445,7 @@
         <v>45576</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19518,7 +19518,7 @@
         <v>45602</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19591,7 +19591,7 @@
         <v>45020</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>45020</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19737,7 +19737,7 @@
         <v>45099</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19810,7 +19810,7 @@
         <v>45638</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19883,7 +19883,7 @@
         <v>45706</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
         <v>45621</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>45621</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20102,7 +20102,7 @@
         <v>45621</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20175,7 +20175,7 @@
         <v>45429</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20248,7 +20248,7 @@
         <v>45580</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20321,7 +20321,7 @@
         <v>45119</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20394,7 +20394,7 @@
         <v>45119</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20467,7 +20467,7 @@
         <v>45356</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20540,7 +20540,7 @@
         <v>45576</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20613,7 +20613,7 @@
         <v>45621</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20686,7 +20686,7 @@
         <v>45111</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20759,7 +20759,7 @@
         <v>44571</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20832,7 +20832,7 @@
         <v>45450</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20905,7 +20905,7 @@
         <v>45106</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20978,7 +20978,7 @@
         <v>45617</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21051,7 +21051,7 @@
         <v>45638</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21124,7 +21124,7 @@
         <v>44783</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21202,7 +21202,7 @@
         <v>45597</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21280,7 +21280,7 @@
         <v>45099</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21353,7 +21353,7 @@
         <v>45687</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>45220</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21499,7 +21499,7 @@
         <v>45620</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21572,7 +21572,7 @@
         <v>45152</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21645,7 +21645,7 @@
         <v>45120</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21718,7 +21718,7 @@
         <v>45120</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21791,7 +21791,7 @@
         <v>45183</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21864,7 +21864,7 @@
         <v>45188</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>45760</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>45734</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22083,7 +22083,7 @@
         <v>45242</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22161,7 +22161,7 @@
         <v>45475</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22234,7 +22234,7 @@
         <v>45475</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22307,7 +22307,7 @@
         <v>45212</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22380,7 +22380,7 @@
         <v>45271</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22453,7 +22453,7 @@
         <v>45278</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22526,7 +22526,7 @@
         <v>44896</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22599,7 +22599,7 @@
         <v>44575</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22672,7 +22672,7 @@
         <v>44909</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22745,7 +22745,7 @@
         <v>45030</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22818,7 +22818,7 @@
         <v>44801</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22891,7 +22891,7 @@
         <v>45271</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22964,7 +22964,7 @@
         <v>45712</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23037,7 +23037,7 @@
         <v>45712</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23110,7 +23110,7 @@
         <v>45712</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23183,7 +23183,7 @@
         <v>45737</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>

--- a/Översikt HABO.xlsx
+++ b/Översikt HABO.xlsx
@@ -601,7 +601,7 @@
         <v>45337</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>44607</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
         <v>44749</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>45534</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>45791</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45635</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>45183</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>45882</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>44877</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>45106</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>45419</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>44749</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>45811</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>45534</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>45631</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>44824</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>45930</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>45225</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>45635</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>45882</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>44801</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>45933</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>45985</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         <v>45597</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>45747</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>45813</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         <v>45882</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>45543</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>45635</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>45635</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>45183</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4027,7 +4027,7 @@
         <v>44749</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>44799</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>45355</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>44847</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>44527</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44769</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>44846</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>44693</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         <v>44877</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>44693</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>44640</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>44670</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>44859</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>44727</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         <v>44500</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>44623</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>45887</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         <v>45882</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         <v>44799</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         <v>44749</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5603,7 +5603,7 @@
         <v>44749</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>45896</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5749,7 +5749,7 @@
         <v>44995</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>45203</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         <v>45595</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>45903</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         <v>44797</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>44944</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>45152</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>45595</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         <v>44913</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>45996</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         <v>45922</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6552,7 +6552,7 @@
         <v>45996</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6625,7 +6625,7 @@
         <v>45922</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         <v>45698</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>45926</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>45698</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>45931</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         <v>45030</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>45120</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7136,7 +7136,7 @@
         <v>45120</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>46171</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         <v>45218</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>45363</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>45400</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
         <v>45620</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>44628</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>46176</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>45478</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         <v>45390</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>45450</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         <v>45450</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>45641</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>45950</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>45091</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>45091</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>45951</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         <v>45204</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         <v>45750</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         <v>44775</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8596,7 +8596,7 @@
         <v>45595</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         <v>45307</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8742,7 +8742,7 @@
         <v>45635</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         <v>46191</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
         <v>45222</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         <v>46191</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9034,7 +9034,7 @@
         <v>46191</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9107,7 +9107,7 @@
         <v>45972</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         <v>45974</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>45470</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9326,7 +9326,7 @@
         <v>45372</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
         <v>46203</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9472,7 +9472,7 @@
         <v>46202</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         <v>44877</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9618,7 +9618,7 @@
         <v>46203</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9691,7 +9691,7 @@
         <v>45985</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9769,7 +9769,7 @@
         <v>45985</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
         <v>45475</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9920,7 +9920,7 @@
         <v>45982</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9993,7 +9993,7 @@
         <v>45217</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10066,7 +10066,7 @@
         <v>45316</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10139,7 +10139,7 @@
         <v>45594</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>45644</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
         <v>45594</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
         <v>46216</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10431,7 +10431,7 @@
         <v>45469</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10509,7 +10509,7 @@
         <v>45400</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10582,7 +10582,7 @@
         <v>46000</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10655,7 +10655,7 @@
         <v>46000</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
         <v>46000</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10801,7 +10801,7 @@
         <v>45777</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>45777</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10947,7 +10947,7 @@
         <v>46000</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>46232</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11093,7 +11093,7 @@
         <v>45789</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11166,7 +11166,7 @@
         <v>45608</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11239,7 +11239,7 @@
         <v>46037</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11312,7 +11312,7 @@
         <v>46037</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11385,7 +11385,7 @@
         <v>46037</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11458,7 +11458,7 @@
         <v>46041</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         <v>46244</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         <v>46043</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>46043</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11750,7 +11750,7 @@
         <v>45021</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11823,7 +11823,7 @@
         <v>46043</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11896,7 +11896,7 @@
         <v>46043</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11969,7 +11969,7 @@
         <v>46043</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12042,7 +12042,7 @@
         <v>46043</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12115,7 +12115,7 @@
         <v>45364</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12188,7 +12188,7 @@
         <v>45734</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
         <v>46052</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12334,7 +12334,7 @@
         <v>46246</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12407,7 +12407,7 @@
         <v>45807</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>46059</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
         <v>45812</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
         <v>45810</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12699,7 +12699,7 @@
         <v>45469</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>45811</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12845,7 +12845,7 @@
         <v>46251</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12918,7 +12918,7 @@
         <v>45827</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12991,7 +12991,7 @@
         <v>45827</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13064,7 +13064,7 @@
         <v>45620</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13137,7 +13137,7 @@
         <v>46254</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13210,7 +13210,7 @@
         <v>44939</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
         <v>46246</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13356,7 +13356,7 @@
         <v>45846</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13429,7 +13429,7 @@
         <v>45810</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13502,7 +13502,7 @@
         <v>45635</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13575,7 +13575,7 @@
         <v>45751</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13648,7 +13648,7 @@
         <v>45877</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13721,7 +13721,7 @@
         <v>45882</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13794,7 +13794,7 @@
         <v>45882</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13872,7 +13872,7 @@
         <v>45882</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>45597</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14023,7 +14023,7 @@
         <v>45646</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14096,7 +14096,7 @@
         <v>46135</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14169,7 +14169,7 @@
         <v>45560</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14242,7 +14242,7 @@
         <v>45677</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14315,7 +14315,7 @@
         <v>44628</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14388,7 +14388,7 @@
         <v>46267</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14461,7 +14461,7 @@
         <v>46267</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14534,7 +14534,7 @@
         <v>46310</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14607,7 +14607,7 @@
         <v>45698</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14680,7 +14680,7 @@
         <v>45820</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14753,7 +14753,7 @@
         <v>46268</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14826,7 +14826,7 @@
         <v>45671</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14899,7 +14899,7 @@
         <v>46268</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14972,7 +14972,7 @@
         <v>46268</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15045,7 +15045,7 @@
         <v>45636</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15118,7 +15118,7 @@
         <v>46273</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>46273</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15274,7 +15274,7 @@
         <v>46315</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15352,7 +15352,7 @@
         <v>45595</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15425,7 +15425,7 @@
         <v>45595</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15498,7 +15498,7 @@
         <v>44749</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15571,7 +15571,7 @@
         <v>44995</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15644,7 +15644,7 @@
         <v>45246</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>45210</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15790,7 +15790,7 @@
         <v>45554</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15863,7 +15863,7 @@
         <v>44914</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>44816</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16009,7 +16009,7 @@
         <v>45733</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16082,7 +16082,7 @@
         <v>45597</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16160,7 +16160,7 @@
         <v>45926</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16233,7 +16233,7 @@
         <v>45107</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16306,7 +16306,7 @@
         <v>45119</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16379,7 +16379,7 @@
         <v>45119</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16452,7 +16452,7 @@
         <v>45120</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>45146</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16598,7 +16598,7 @@
         <v>45660</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16671,7 +16671,7 @@
         <v>45647</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16744,7 +16744,7 @@
         <v>45478</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16817,7 +16817,7 @@
         <v>45450</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16890,7 +16890,7 @@
         <v>45450</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16963,7 +16963,7 @@
         <v>45698</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17036,7 +17036,7 @@
         <v>45687</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17109,7 +17109,7 @@
         <v>45757</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17182,7 +17182,7 @@
         <v>45757</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17255,7 +17255,7 @@
         <v>45111</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17328,7 +17328,7 @@
         <v>45621</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17401,7 +17401,7 @@
         <v>45621</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17474,7 +17474,7 @@
         <v>45113</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         <v>44830</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17620,7 +17620,7 @@
         <v>45007</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17693,7 +17693,7 @@
         <v>45751</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17766,7 +17766,7 @@
         <v>45173</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17839,7 +17839,7 @@
         <v>44876</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17912,7 +17912,7 @@
         <v>44845</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17985,7 +17985,7 @@
         <v>44894</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>45620</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18131,7 +18131,7 @@
         <v>45091</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18204,7 +18204,7 @@
         <v>44749</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18277,7 +18277,7 @@
         <v>45236</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18350,7 +18350,7 @@
         <v>45631</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18423,7 +18423,7 @@
         <v>45558</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18496,7 +18496,7 @@
         <v>45099</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18569,7 +18569,7 @@
         <v>45636</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18642,7 +18642,7 @@
         <v>45120</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>45287</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>45020</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18861,7 +18861,7 @@
         <v>45397</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>44951</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19007,7 +19007,7 @@
         <v>45029</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19080,7 +19080,7 @@
         <v>45419</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19153,7 +19153,7 @@
         <v>45149</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>45510</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19299,7 +19299,7 @@
         <v>45475</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19372,7 +19372,7 @@
         <v>45121</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19445,7 +19445,7 @@
         <v>45576</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19518,7 +19518,7 @@
         <v>45602</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19591,7 +19591,7 @@
         <v>45020</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>45020</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19737,7 +19737,7 @@
         <v>45099</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19810,7 +19810,7 @@
         <v>45638</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19883,7 +19883,7 @@
         <v>45706</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
         <v>45621</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>45621</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20102,7 +20102,7 @@
         <v>45621</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20175,7 +20175,7 @@
         <v>45429</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20248,7 +20248,7 @@
         <v>45580</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20321,7 +20321,7 @@
         <v>45119</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20394,7 +20394,7 @@
         <v>45119</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20467,7 +20467,7 @@
         <v>45356</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20540,7 +20540,7 @@
         <v>45576</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20613,7 +20613,7 @@
         <v>45621</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20686,7 +20686,7 @@
         <v>45111</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20759,7 +20759,7 @@
         <v>44571</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20832,7 +20832,7 @@
         <v>45450</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20905,7 +20905,7 @@
         <v>45106</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20978,7 +20978,7 @@
         <v>45617</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21051,7 +21051,7 @@
         <v>45638</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21124,7 +21124,7 @@
         <v>44783</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21202,7 +21202,7 @@
         <v>45597</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21280,7 +21280,7 @@
         <v>45099</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21353,7 +21353,7 @@
         <v>45687</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>45220</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21499,7 +21499,7 @@
         <v>45620</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21572,7 +21572,7 @@
         <v>45152</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21645,7 +21645,7 @@
         <v>45120</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21718,7 +21718,7 @@
         <v>45120</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21791,7 +21791,7 @@
         <v>45183</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21864,7 +21864,7 @@
         <v>45188</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>45760</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>45734</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22083,7 +22083,7 @@
         <v>45242</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22161,7 +22161,7 @@
         <v>45475</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22234,7 +22234,7 @@
         <v>45475</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22307,7 +22307,7 @@
         <v>45212</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22380,7 +22380,7 @@
         <v>45271</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22453,7 +22453,7 @@
         <v>45278</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22526,7 +22526,7 @@
         <v>44896</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22599,7 +22599,7 @@
         <v>44575</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22672,7 +22672,7 @@
         <v>44909</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22745,7 +22745,7 @@
         <v>45030</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22818,7 +22818,7 @@
         <v>44801</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22891,7 +22891,7 @@
         <v>45271</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22964,7 +22964,7 @@
         <v>45712</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23037,7 +23037,7 @@
         <v>45712</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23110,7 +23110,7 @@
         <v>45712</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23183,7 +23183,7 @@
         <v>45737</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
